--- a/research/traditional_assets/database/data/australia/australia_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_telecom_equipment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,13 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.2383378136962097</v>
+      </c>
+      <c r="C2">
+        <v>3.238264176075444</v>
+      </c>
+      <c r="D2">
+        <v>1.206374176075445</v>
       </c>
       <c r="E2">
-        <v>-0.331</v>
+        <v>-0.29289</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.03811</v>
       </c>
       <c r="G2">
         <v>2.07</v>
@@ -1430,43 +1439,45 @@
         <v>-1.462</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008986338</v>
       </c>
       <c r="N2">
-        <v>-1.462</v>
+        <v>-1.470986338</v>
       </c>
       <c r="O2">
-        <v>-0.4386</v>
+        <v>-0.4412959014</v>
       </c>
       <c r="P2">
-        <v>-1.0234</v>
+        <v>-1.0296904366</v>
       </c>
       <c r="Q2">
-        <v>0.7565999999999999</v>
+        <v>0.7503095634000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.1221130406654462</v>
+      </c>
+      <c r="T2">
+        <v>1.76242588141908</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-48.80742300144953</v>
+      </c>
+      <c r="W2">
+        <v>11.7445903437418</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-162.6914100048318</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1474,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2383378136962097</v>
+        <v>0.2402378136962097</v>
       </c>
       <c r="C3">
-        <v>3.238264176075444</v>
+        <v>3.195270922809009</v>
       </c>
       <c r="D3">
-        <v>1.206374176075445</v>
+        <v>1.201490922809009</v>
       </c>
       <c r="E3">
-        <v>-0.29289</v>
+        <v>-0.25478</v>
       </c>
       <c r="F3">
-        <v>0.03811</v>
+        <v>0.07622</v>
       </c>
       <c r="G3">
         <v>2.07</v>
@@ -1510,37 +1521,37 @@
         <v>-1.462</v>
       </c>
       <c r="M3">
-        <v>0.008986338</v>
+        <v>0.017972676</v>
       </c>
       <c r="N3">
-        <v>-1.470986338</v>
+        <v>-1.479972676</v>
       </c>
       <c r="O3">
-        <v>-0.4412959014</v>
+        <v>-0.4439918028</v>
       </c>
       <c r="P3">
-        <v>-1.0296904366</v>
+        <v>-1.0359808732</v>
       </c>
       <c r="Q3">
-        <v>0.7503095634000001</v>
+        <v>0.7440191268</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1221130406654462</v>
+        <v>0.1228917451620324</v>
       </c>
       <c r="T3">
-        <v>1.76242588141908</v>
+        <v>1.780409818984581</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-48.80742300144953</v>
+        <v>-24.40371150072476</v>
       </c>
       <c r="W3">
-        <v>11.7445903437418</v>
+        <v>5.9901951718709</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1548,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-162.6914100048318</v>
+        <v>-81.3457050024159</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1556,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2402378136962097</v>
+        <v>0.2421378136962097</v>
       </c>
       <c r="C4">
-        <v>3.195270922809009</v>
+        <v>3.152317043769532</v>
       </c>
       <c r="D4">
-        <v>1.201490922809009</v>
+        <v>1.196647043769532</v>
       </c>
       <c r="E4">
-        <v>-0.25478</v>
+        <v>-0.21667</v>
       </c>
       <c r="F4">
-        <v>0.07622</v>
+        <v>0.11433</v>
       </c>
       <c r="G4">
         <v>2.07</v>
@@ -1592,37 +1603,37 @@
         <v>-1.462</v>
       </c>
       <c r="M4">
-        <v>0.017972676</v>
+        <v>0.026959014</v>
       </c>
       <c r="N4">
-        <v>-1.479972676</v>
+        <v>-1.488959014</v>
       </c>
       <c r="O4">
-        <v>-0.4439918028</v>
+        <v>-0.4466877042</v>
       </c>
       <c r="P4">
-        <v>-1.0359808732</v>
+        <v>-1.0422713098</v>
       </c>
       <c r="Q4">
-        <v>0.7440191268</v>
+        <v>0.7377286902</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1228917451620324</v>
+        <v>0.1236865054214348</v>
       </c>
       <c r="T4">
-        <v>1.780409818984581</v>
+        <v>1.798764559386484</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-24.40371150072476</v>
+        <v>-16.26914100048318</v>
       </c>
       <c r="W4">
-        <v>5.9901951718709</v>
+        <v>4.072063447913933</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1630,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-81.3457050024159</v>
+        <v>-54.2304700016106</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1638,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2421378136962097</v>
+        <v>0.2440378136962097</v>
       </c>
       <c r="C5">
-        <v>3.152317043769532</v>
+        <v>3.109402064650894</v>
       </c>
       <c r="D5">
-        <v>1.196647043769532</v>
+        <v>1.191842064650894</v>
       </c>
       <c r="E5">
-        <v>-0.21667</v>
+        <v>-0.17856</v>
       </c>
       <c r="F5">
-        <v>0.11433</v>
+        <v>0.15244</v>
       </c>
       <c r="G5">
         <v>2.07</v>
@@ -1674,37 +1685,37 @@
         <v>-1.462</v>
       </c>
       <c r="M5">
-        <v>0.026959014</v>
+        <v>0.035945352</v>
       </c>
       <c r="N5">
-        <v>-1.488959014</v>
+        <v>-1.497945352</v>
       </c>
       <c r="O5">
-        <v>-0.4466877042</v>
+        <v>-0.4493836056</v>
       </c>
       <c r="P5">
-        <v>-1.0422713098</v>
+        <v>-1.0485617464</v>
       </c>
       <c r="Q5">
-        <v>0.7377286902</v>
+        <v>0.7314382536000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1236865054214348</v>
+        <v>0.1244978231862414</v>
       </c>
       <c r="T5">
-        <v>1.798764559386484</v>
+        <v>1.817501690213426</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-16.26914100048318</v>
+        <v>-12.20185575036238</v>
       </c>
       <c r="W5">
-        <v>4.072063447913933</v>
+        <v>3.11299758593545</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1712,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-54.2304700016106</v>
+        <v>-40.67285250120794</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1720,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2440378136962097</v>
+        <v>0.2459378136962097</v>
       </c>
       <c r="C6">
-        <v>3.109402064650894</v>
+        <v>3.066525518734566</v>
       </c>
       <c r="D6">
-        <v>1.191842064650894</v>
+        <v>1.187075518734567</v>
       </c>
       <c r="E6">
-        <v>-0.17856</v>
+        <v>-0.14045</v>
       </c>
       <c r="F6">
-        <v>0.15244</v>
+        <v>0.19055</v>
       </c>
       <c r="G6">
         <v>2.07</v>
@@ -1756,37 +1767,37 @@
         <v>-1.462</v>
       </c>
       <c r="M6">
-        <v>0.035945352</v>
+        <v>0.04493169</v>
       </c>
       <c r="N6">
-        <v>-1.497945352</v>
+        <v>-1.50693169</v>
       </c>
       <c r="O6">
-        <v>-0.4493836056</v>
+        <v>-0.452079507</v>
       </c>
       <c r="P6">
-        <v>-1.0485617464</v>
+        <v>-1.054852183</v>
       </c>
       <c r="Q6">
-        <v>0.7314382536000001</v>
+        <v>0.7251478170000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1244978231862414</v>
+        <v>0.1253262213250439</v>
       </c>
       <c r="T6">
-        <v>1.817501690213426</v>
+        <v>1.836633286952515</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-12.20185575036238</v>
+        <v>-9.761484600289906</v>
       </c>
       <c r="W6">
-        <v>3.11299758593545</v>
+        <v>2.53755806874836</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1794,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-40.67285250120794</v>
+        <v>-32.53828200096635</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1802,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2459378136962097</v>
+        <v>0.2478378136962097</v>
       </c>
       <c r="C7">
-        <v>3.066525518734566</v>
+        <v>3.023686946738486</v>
       </c>
       <c r="D7">
-        <v>1.187075518734567</v>
+        <v>1.182346946738486</v>
       </c>
       <c r="E7">
-        <v>-0.14045</v>
+        <v>-0.10234</v>
       </c>
       <c r="F7">
-        <v>0.19055</v>
+        <v>0.22866</v>
       </c>
       <c r="G7">
         <v>2.07</v>
@@ -1838,37 +1849,37 @@
         <v>-1.462</v>
       </c>
       <c r="M7">
-        <v>0.04493169</v>
+        <v>0.053918028</v>
       </c>
       <c r="N7">
-        <v>-1.50693169</v>
+        <v>-1.515918028</v>
       </c>
       <c r="O7">
-        <v>-0.452079507</v>
+        <v>-0.4547754084</v>
       </c>
       <c r="P7">
-        <v>-1.054852183</v>
+        <v>-1.0611426196</v>
       </c>
       <c r="Q7">
-        <v>0.7251478170000001</v>
+        <v>0.7188573804</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1253262213250439</v>
+        <v>0.1261722449561614</v>
       </c>
       <c r="T7">
-        <v>1.836633286952515</v>
+        <v>1.856171938941372</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-9.761484600289906</v>
+        <v>-8.134570500241589</v>
       </c>
       <c r="W7">
-        <v>2.53755806874836</v>
+        <v>2.153931723956967</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1876,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-32.53828200096635</v>
+        <v>-27.1152350008053</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1884,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2478378136962097</v>
+        <v>0.2497378136962097</v>
       </c>
       <c r="C8">
-        <v>3.023686946738486</v>
+        <v>2.980885896669535</v>
       </c>
       <c r="D8">
-        <v>1.182346946738486</v>
+        <v>1.177655896669535</v>
       </c>
       <c r="E8">
-        <v>-0.10234</v>
+        <v>-0.06423000000000006</v>
       </c>
       <c r="F8">
-        <v>0.22866</v>
+        <v>0.26677</v>
       </c>
       <c r="G8">
         <v>2.07</v>
@@ -1920,37 +1931,37 @@
         <v>-1.462</v>
       </c>
       <c r="M8">
-        <v>0.05391802799999999</v>
+        <v>0.06290436599999999</v>
       </c>
       <c r="N8">
-        <v>-1.515918028</v>
+        <v>-1.524904366</v>
       </c>
       <c r="O8">
-        <v>-0.4547754084</v>
+        <v>-0.4574713097999999</v>
       </c>
       <c r="P8">
-        <v>-1.0611426196</v>
+        <v>-1.0674330562</v>
       </c>
       <c r="Q8">
-        <v>0.7188573804</v>
+        <v>0.7125669438</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1261722449561614</v>
+        <v>0.127036462643862</v>
       </c>
       <c r="T8">
-        <v>1.856171938941371</v>
+        <v>1.876130776994504</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-8.134570500241589</v>
+        <v>-6.972489000207077</v>
       </c>
       <c r="W8">
-        <v>2.153931723956967</v>
+        <v>1.879912906248829</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1958,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-27.1152350008053</v>
+        <v>-23.24163000069026</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1966,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2497378136962097</v>
+        <v>0.2516378136962097</v>
       </c>
       <c r="C9">
-        <v>2.980885896669534</v>
+        <v>2.938121923679511</v>
       </c>
       <c r="D9">
-        <v>1.177655896669535</v>
+        <v>1.173001923679512</v>
       </c>
       <c r="E9">
-        <v>-0.06423000000000001</v>
+        <v>-0.02612000000000003</v>
       </c>
       <c r="F9">
-        <v>0.26677</v>
+        <v>0.30488</v>
       </c>
       <c r="G9">
         <v>2.07</v>
@@ -2002,37 +2013,37 @@
         <v>-1.462</v>
       </c>
       <c r="M9">
-        <v>0.062904366</v>
+        <v>0.071890704</v>
       </c>
       <c r="N9">
-        <v>-1.524904366</v>
+        <v>-1.533890704</v>
       </c>
       <c r="O9">
-        <v>-0.4574713097999999</v>
+        <v>-0.4601672112</v>
       </c>
       <c r="P9">
-        <v>-1.0674330562</v>
+        <v>-1.0737234928</v>
       </c>
       <c r="Q9">
-        <v>0.7125669438</v>
+        <v>0.7062765071999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1270364626438621</v>
+        <v>0.1279194676725997</v>
       </c>
       <c r="T9">
-        <v>1.876130776994505</v>
+        <v>1.896523502831401</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-6.972489000207076</v>
+        <v>-6.100927875181191</v>
       </c>
       <c r="W9">
-        <v>1.879912906248828</v>
+        <v>1.674398792967725</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2040,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-23.24163000069025</v>
+        <v>-20.33642625060397</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2048,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2516378136962097</v>
+        <v>0.2535378136962097</v>
       </c>
       <c r="C10">
-        <v>2.938121923679511</v>
+        <v>2.895394589924511</v>
       </c>
       <c r="D10">
-        <v>1.173001923679512</v>
+        <v>1.168384589924511</v>
       </c>
       <c r="E10">
-        <v>-0.02612000000000003</v>
+        <v>0.01198999999999995</v>
       </c>
       <c r="F10">
-        <v>0.30488</v>
+        <v>0.34299</v>
       </c>
       <c r="G10">
         <v>2.07</v>
@@ -2084,37 +2095,37 @@
         <v>-1.462</v>
       </c>
       <c r="M10">
-        <v>0.071890704</v>
+        <v>0.080877042</v>
       </c>
       <c r="N10">
-        <v>-1.533890704</v>
+        <v>-1.542877042</v>
       </c>
       <c r="O10">
-        <v>-0.4601672112</v>
+        <v>-0.4628631126</v>
       </c>
       <c r="P10">
-        <v>-1.0737234928</v>
+        <v>-1.0800139294</v>
       </c>
       <c r="Q10">
-        <v>0.7062765071999999</v>
+        <v>0.6999860706000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1279194676725997</v>
+        <v>0.1288218794052656</v>
       </c>
       <c r="T10">
-        <v>1.896523502831401</v>
+        <v>1.917364420444933</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-6.100927875181191</v>
+        <v>-5.423047000161059</v>
       </c>
       <c r="W10">
-        <v>1.674398792967725</v>
+        <v>1.514554482637978</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2122,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-20.33642625060397</v>
+        <v>-18.0768233338702</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2130,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2535378136962097</v>
+        <v>0.2554378136962097</v>
       </c>
       <c r="C11">
-        <v>2.895394589924511</v>
+        <v>2.852703464427605</v>
       </c>
       <c r="D11">
-        <v>1.168384589924511</v>
+        <v>1.163803464427605</v>
       </c>
       <c r="E11">
-        <v>0.01198999999999995</v>
+        <v>0.05009999999999992</v>
       </c>
       <c r="F11">
-        <v>0.34299</v>
+        <v>0.3810999999999999</v>
       </c>
       <c r="G11">
         <v>2.07</v>
@@ -2166,37 +2177,37 @@
         <v>-1.462</v>
       </c>
       <c r="M11">
-        <v>0.080877042</v>
+        <v>0.08986337999999999</v>
       </c>
       <c r="N11">
-        <v>-1.542877042</v>
+        <v>-1.55186338</v>
       </c>
       <c r="O11">
-        <v>-0.4628631126</v>
+        <v>-0.4655590139999999</v>
       </c>
       <c r="P11">
-        <v>-1.0800139294</v>
+        <v>-1.086304366</v>
       </c>
       <c r="Q11">
-        <v>0.6999860706000001</v>
+        <v>0.693695634</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1288218794052656</v>
+        <v>0.1297443447319908</v>
       </c>
       <c r="T11">
-        <v>1.917364420444933</v>
+        <v>1.938668469560987</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-5.423047000161059</v>
+        <v>-4.880742300144953</v>
       </c>
       <c r="W11">
-        <v>1.514554482637978</v>
+        <v>1.38667903437418</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2204,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-18.0768233338702</v>
+        <v>-16.26914100048318</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2212,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2554378136962097</v>
+        <v>0.2573378136962097</v>
       </c>
       <c r="C12">
-        <v>2.852703464427605</v>
+        <v>2.810048122944745</v>
       </c>
       <c r="D12">
-        <v>1.163803464427605</v>
+        <v>1.159258122944745</v>
       </c>
       <c r="E12">
-        <v>0.05009999999999998</v>
+        <v>0.08820999999999996</v>
       </c>
       <c r="F12">
-        <v>0.3811</v>
+        <v>0.41921</v>
       </c>
       <c r="G12">
         <v>2.07</v>
@@ -2248,37 +2259,37 @@
         <v>-1.462</v>
       </c>
       <c r="M12">
-        <v>0.08986338000000001</v>
+        <v>0.098849718</v>
       </c>
       <c r="N12">
-        <v>-1.55186338</v>
+        <v>-1.560849718</v>
       </c>
       <c r="O12">
-        <v>-0.4655590139999999</v>
+        <v>-0.4682549154</v>
       </c>
       <c r="P12">
-        <v>-1.086304366</v>
+        <v>-1.0925948026</v>
       </c>
       <c r="Q12">
-        <v>0.693695634</v>
+        <v>0.6874051973999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1297443447319908</v>
+        <v>0.1306875396166199</v>
       </c>
       <c r="T12">
-        <v>1.938668469560988</v>
+        <v>1.960451261353808</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-4.880742300144953</v>
+        <v>-4.437038454677229</v>
       </c>
       <c r="W12">
-        <v>1.38667903437418</v>
+        <v>1.282053667612891</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2286,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-16.26914100048317</v>
+        <v>-14.79012818225744</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2294,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2573378136962097</v>
+        <v>0.2592378136962097</v>
       </c>
       <c r="C13">
-        <v>2.810048122944745</v>
+        <v>2.767428147833797</v>
       </c>
       <c r="D13">
-        <v>1.159258122944745</v>
+        <v>1.154748147833797</v>
       </c>
       <c r="E13">
-        <v>0.08820999999999996</v>
+        <v>0.1263199999999999</v>
       </c>
       <c r="F13">
-        <v>0.41921</v>
+        <v>0.4573199999999999</v>
       </c>
       <c r="G13">
         <v>2.07</v>
@@ -2330,37 +2341,37 @@
         <v>-1.462</v>
       </c>
       <c r="M13">
-        <v>0.098849718</v>
+        <v>0.107836056</v>
       </c>
       <c r="N13">
-        <v>-1.560849718</v>
+        <v>-1.569836056</v>
       </c>
       <c r="O13">
-        <v>-0.4682549154</v>
+        <v>-0.4709508167999999</v>
       </c>
       <c r="P13">
-        <v>-1.0925948026</v>
+        <v>-1.0988852392</v>
       </c>
       <c r="Q13">
-        <v>0.6874051973999999</v>
+        <v>0.6811147608000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1306875396166199</v>
+        <v>0.1316521707486269</v>
       </c>
       <c r="T13">
-        <v>1.960451261353808</v>
+        <v>1.982729116596465</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-4.437038454677229</v>
+        <v>-4.067285250120794</v>
       </c>
       <c r="W13">
-        <v>1.282053667612891</v>
+        <v>1.194865861978483</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2368,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-14.79012818225744</v>
+        <v>-13.55761750040265</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2376,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2592378136962097</v>
+        <v>0.2611378136962097</v>
       </c>
       <c r="C14">
-        <v>2.767428147833797</v>
+        <v>2.724843127926613</v>
       </c>
       <c r="D14">
-        <v>1.154748147833797</v>
+        <v>1.150273127926613</v>
       </c>
       <c r="E14">
-        <v>0.1263199999999999</v>
+        <v>0.16443</v>
       </c>
       <c r="F14">
-        <v>0.4573199999999999</v>
+        <v>0.49543</v>
       </c>
       <c r="G14">
         <v>2.07</v>
@@ -2412,37 +2423,37 @@
         <v>-1.462</v>
       </c>
       <c r="M14">
-        <v>0.107836056</v>
+        <v>0.116822394</v>
       </c>
       <c r="N14">
-        <v>-1.569836056</v>
+        <v>-1.578822394</v>
       </c>
       <c r="O14">
-        <v>-0.4709508167999999</v>
+        <v>-0.4736467181999999</v>
       </c>
       <c r="P14">
-        <v>-1.0988852392</v>
+        <v>-1.1051756758</v>
       </c>
       <c r="Q14">
-        <v>0.6811147608000001</v>
+        <v>0.6748243242</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1316521707486269</v>
+        <v>0.132638977308956</v>
       </c>
       <c r="T14">
-        <v>1.982729116596465</v>
+        <v>2.005519106442401</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-4.067285250120794</v>
+        <v>-3.754417153957656</v>
       </c>
       <c r="W14">
-        <v>1.194865861978483</v>
+        <v>1.121091564903215</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2450,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-13.55761750040265</v>
+        <v>-12.51472384652552</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2458,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2611378136962097</v>
+        <v>0.2630378136962097</v>
       </c>
       <c r="C15">
-        <v>2.724843127926613</v>
+        <v>2.682292658404078</v>
       </c>
       <c r="D15">
-        <v>1.150273127926613</v>
+        <v>1.145832658404078</v>
       </c>
       <c r="E15">
-        <v>0.16443</v>
+        <v>0.20254</v>
       </c>
       <c r="F15">
-        <v>0.49543</v>
+        <v>0.53354</v>
       </c>
       <c r="G15">
         <v>2.07</v>
@@ -2494,37 +2505,37 @@
         <v>-1.462</v>
       </c>
       <c r="M15">
-        <v>0.116822394</v>
+        <v>0.125808732</v>
       </c>
       <c r="N15">
-        <v>-1.578822394</v>
+        <v>-1.587808732</v>
       </c>
       <c r="O15">
-        <v>-0.4736467181999999</v>
+        <v>-0.4763426196</v>
       </c>
       <c r="P15">
-        <v>-1.1051756758</v>
+        <v>-1.1114661124</v>
       </c>
       <c r="Q15">
-        <v>0.6748243242</v>
+        <v>0.6685338876</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.132638977308956</v>
+        <v>0.1336487328590601</v>
       </c>
       <c r="T15">
-        <v>2.005519106442401</v>
+        <v>2.028839096052196</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-3.754417153957656</v>
+        <v>-3.486244500103538</v>
       </c>
       <c r="W15">
-        <v>1.121091564903215</v>
+        <v>1.057856453124414</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2532,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-12.51472384652552</v>
+        <v>-11.62081500034513</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2540,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2630378136962097</v>
+        <v>0.2649378136962097</v>
       </c>
       <c r="C16">
-        <v>2.682292658404078</v>
+        <v>2.63977634067403</v>
       </c>
       <c r="D16">
-        <v>1.145832658404078</v>
+        <v>1.14142634067403</v>
       </c>
       <c r="E16">
-        <v>0.20254</v>
+        <v>0.2406500000000001</v>
       </c>
       <c r="F16">
-        <v>0.53354</v>
+        <v>0.5716500000000001</v>
       </c>
       <c r="G16">
         <v>2.07</v>
@@ -2576,37 +2587,37 @@
         <v>-1.462</v>
       </c>
       <c r="M16">
-        <v>0.125808732</v>
+        <v>0.13479507</v>
       </c>
       <c r="N16">
-        <v>-1.587808732</v>
+        <v>-1.59679507</v>
       </c>
       <c r="O16">
-        <v>-0.4763426196</v>
+        <v>-0.479038521</v>
       </c>
       <c r="P16">
-        <v>-1.1114661124</v>
+        <v>-1.117756549</v>
       </c>
       <c r="Q16">
-        <v>0.6685338876</v>
+        <v>0.6622434509999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1336487328590601</v>
+        <v>0.1346822473632844</v>
       </c>
       <c r="T16">
-        <v>2.028839096052196</v>
+        <v>2.052707791299869</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-3.486244500103538</v>
+        <v>-3.253828200096635</v>
       </c>
       <c r="W16">
-        <v>1.057856453124414</v>
+        <v>1.003052689582786</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2614,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-11.62081500034513</v>
+        <v>-10.84609400032212</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2622,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2649378136962097</v>
+        <v>0.2668378136962097</v>
       </c>
       <c r="C17">
-        <v>2.63977634067403</v>
+        <v>2.597293782251988</v>
       </c>
       <c r="D17">
-        <v>1.14142634067403</v>
+        <v>1.137053782251988</v>
       </c>
       <c r="E17">
-        <v>0.24065</v>
+        <v>0.27876</v>
       </c>
       <c r="F17">
-        <v>0.57165</v>
+        <v>0.60976</v>
       </c>
       <c r="G17">
         <v>2.07</v>
@@ -2658,37 +2669,37 @@
         <v>-1.462</v>
       </c>
       <c r="M17">
-        <v>0.13479507</v>
+        <v>0.143781408</v>
       </c>
       <c r="N17">
-        <v>-1.59679507</v>
+        <v>-1.605781408</v>
       </c>
       <c r="O17">
-        <v>-0.479038521</v>
+        <v>-0.4817344224</v>
       </c>
       <c r="P17">
-        <v>-1.117756549</v>
+        <v>-1.1240469856</v>
       </c>
       <c r="Q17">
-        <v>0.6622434509999999</v>
+        <v>0.6559530144000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1346822473632844</v>
+        <v>0.1357403693557044</v>
       </c>
       <c r="T17">
-        <v>2.052707791299869</v>
+        <v>2.077144788815344</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-3.253828200096635</v>
+        <v>-3.050463937590596</v>
       </c>
       <c r="W17">
-        <v>1.003052689582786</v>
+        <v>0.9550993964838626</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2696,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-10.84609400032212</v>
+        <v>-10.16821312530199</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2704,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2668378136962097</v>
+        <v>0.2687378136962097</v>
       </c>
       <c r="C18">
-        <v>2.597293782251988</v>
+        <v>2.554844596644615</v>
       </c>
       <c r="D18">
-        <v>1.137053782251988</v>
+        <v>1.132714596644615</v>
       </c>
       <c r="E18">
-        <v>0.27876</v>
+        <v>0.31687</v>
       </c>
       <c r="F18">
-        <v>0.60976</v>
+        <v>0.6478700000000001</v>
       </c>
       <c r="G18">
         <v>2.07</v>
@@ -2740,37 +2751,37 @@
         <v>-1.462</v>
       </c>
       <c r="M18">
-        <v>0.143781408</v>
+        <v>0.152767746</v>
       </c>
       <c r="N18">
-        <v>-1.605781408</v>
+        <v>-1.614767746</v>
       </c>
       <c r="O18">
-        <v>-0.4817344224</v>
+        <v>-0.4844303238</v>
       </c>
       <c r="P18">
-        <v>-1.1240469856</v>
+        <v>-1.1303374222</v>
       </c>
       <c r="Q18">
-        <v>0.6559530144000001</v>
+        <v>0.6496625778</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1357403693557044</v>
+        <v>0.1368239882636045</v>
       </c>
       <c r="T18">
-        <v>2.077144788815344</v>
+        <v>2.102170629644445</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-3.050463937590596</v>
+        <v>-2.871024882438208</v>
       </c>
       <c r="W18">
-        <v>0.9550993964838626</v>
+        <v>0.9127876672789293</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2778,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-10.16821312530199</v>
+        <v>-9.570082941460692</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2786,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2687378136962097</v>
+        <v>0.2706378136962097</v>
       </c>
       <c r="C19">
-        <v>2.554844596644615</v>
+        <v>2.512428403235838</v>
       </c>
       <c r="D19">
-        <v>1.132714596644615</v>
+        <v>1.128408403235838</v>
       </c>
       <c r="E19">
-        <v>0.31687</v>
+        <v>0.35498</v>
       </c>
       <c r="F19">
-        <v>0.6478700000000001</v>
+        <v>0.68598</v>
       </c>
       <c r="G19">
         <v>2.07</v>
@@ -2822,37 +2833,37 @@
         <v>-1.462</v>
       </c>
       <c r="M19">
-        <v>0.152767746</v>
+        <v>0.161754084</v>
       </c>
       <c r="N19">
-        <v>-1.614767746</v>
+        <v>-1.623754084</v>
       </c>
       <c r="O19">
-        <v>-0.4844303238</v>
+        <v>-0.4871262252</v>
       </c>
       <c r="P19">
-        <v>-1.1303374222</v>
+        <v>-1.1366278588</v>
       </c>
       <c r="Q19">
-        <v>0.6496625778</v>
+        <v>0.6433721412</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1368239882636045</v>
+        <v>0.1379340369009655</v>
       </c>
       <c r="T19">
-        <v>2.102170629644445</v>
+        <v>2.12780685683523</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-2.871024882438208</v>
+        <v>-2.711523500080529</v>
       </c>
       <c r="W19">
-        <v>0.9127876672789293</v>
+        <v>0.8751772413189888</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2860,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-9.570082941460692</v>
+        <v>-9.038411666935097</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2868,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2706378136962097</v>
+        <v>0.2725378136962097</v>
       </c>
       <c r="C20">
-        <v>2.512428403235838</v>
+        <v>2.470044827175549</v>
       </c>
       <c r="D20">
-        <v>1.128408403235838</v>
+        <v>1.124134827175549</v>
       </c>
       <c r="E20">
-        <v>0.3549799999999999</v>
+        <v>0.39309</v>
       </c>
       <c r="F20">
-        <v>0.6859799999999999</v>
+        <v>0.72409</v>
       </c>
       <c r="G20">
         <v>2.07</v>
@@ -2904,37 +2915,37 @@
         <v>-1.462</v>
       </c>
       <c r="M20">
-        <v>0.161754084</v>
+        <v>0.170740422</v>
       </c>
       <c r="N20">
-        <v>-1.623754084</v>
+        <v>-1.632740422</v>
       </c>
       <c r="O20">
-        <v>-0.4871262252</v>
+        <v>-0.4898221266</v>
       </c>
       <c r="P20">
-        <v>-1.1366278588</v>
+        <v>-1.1429182954</v>
       </c>
       <c r="Q20">
-        <v>0.6433721412</v>
+        <v>0.6370817046000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1379340369009655</v>
+        <v>0.1390714941466564</v>
       </c>
       <c r="T20">
-        <v>2.12780685683523</v>
+        <v>2.154076077289986</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-2.71152350008053</v>
+        <v>-2.568811736918396</v>
       </c>
       <c r="W20">
-        <v>0.8751772413189889</v>
+        <v>0.8415258075653579</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2942,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-9.038411666935099</v>
+        <v>-8.562705789727987</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2950,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2725378136962097</v>
+        <v>0.2744378136962097</v>
       </c>
       <c r="C21">
-        <v>2.470044827175549</v>
+        <v>2.427693499270835</v>
       </c>
       <c r="D21">
-        <v>1.124134827175549</v>
+        <v>1.119893499270835</v>
       </c>
       <c r="E21">
-        <v>0.39309</v>
+        <v>0.4312</v>
       </c>
       <c r="F21">
-        <v>0.72409</v>
+        <v>0.7622</v>
       </c>
       <c r="G21">
         <v>2.07</v>
@@ -2986,37 +2997,37 @@
         <v>-1.462</v>
       </c>
       <c r="M21">
-        <v>0.170740422</v>
+        <v>0.17972676</v>
       </c>
       <c r="N21">
-        <v>-1.632740422</v>
+        <v>-1.64172676</v>
       </c>
       <c r="O21">
-        <v>-0.4898221266</v>
+        <v>-0.492518028</v>
       </c>
       <c r="P21">
-        <v>-1.1429182954</v>
+        <v>-1.149208732</v>
       </c>
       <c r="Q21">
-        <v>0.6370817046000001</v>
+        <v>0.6307912680000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1390714941466564</v>
+        <v>0.1402373878234896</v>
       </c>
       <c r="T21">
-        <v>2.154076077289986</v>
+        <v>2.181002028256111</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-2.568811736918396</v>
+        <v>-2.440371150072477</v>
       </c>
       <c r="W21">
-        <v>0.8415258075653579</v>
+        <v>0.81123951718709</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3024,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-8.562705789727987</v>
+        <v>-8.134570500241589</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3032,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2744378136962097</v>
+        <v>0.2763378136962097</v>
       </c>
       <c r="C22">
-        <v>2.427693499270835</v>
+        <v>2.385374055879658</v>
       </c>
       <c r="D22">
-        <v>1.119893499270835</v>
+        <v>1.115684055879659</v>
       </c>
       <c r="E22">
-        <v>0.4312</v>
+        <v>0.4693100000000001</v>
       </c>
       <c r="F22">
-        <v>0.7622</v>
+        <v>0.8003100000000001</v>
       </c>
       <c r="G22">
         <v>2.07</v>
@@ -3068,37 +3079,37 @@
         <v>-1.462</v>
       </c>
       <c r="M22">
-        <v>0.17972676</v>
+        <v>0.188713098</v>
       </c>
       <c r="N22">
-        <v>-1.64172676</v>
+        <v>-1.650713098</v>
       </c>
       <c r="O22">
-        <v>-0.492518028</v>
+        <v>-0.4952139294</v>
       </c>
       <c r="P22">
-        <v>-1.149208732</v>
+        <v>-1.1554991686</v>
       </c>
       <c r="Q22">
-        <v>0.6307912680000001</v>
+        <v>0.6245008314</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1402373878234896</v>
+        <v>0.1414327977959389</v>
       </c>
       <c r="T22">
-        <v>2.181002028256111</v>
+        <v>2.208609648866948</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-2.440371150072477</v>
+        <v>-2.324163000069025</v>
       </c>
       <c r="W22">
-        <v>0.81123951718709</v>
+        <v>0.783837635416276</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3106,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-8.134570500241589</v>
+        <v>-7.747210000230083</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3114,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2763378136962097</v>
+        <v>0.2782378136962097</v>
       </c>
       <c r="C23">
-        <v>2.385374055879658</v>
+        <v>2.343086138806918</v>
       </c>
       <c r="D23">
-        <v>1.115684055879659</v>
+        <v>1.111506138806919</v>
       </c>
       <c r="E23">
-        <v>0.4693099999999999</v>
+        <v>0.50742</v>
       </c>
       <c r="F23">
-        <v>0.80031</v>
+        <v>0.8384199999999999</v>
       </c>
       <c r="G23">
         <v>2.07</v>
@@ -3150,37 +3161,37 @@
         <v>-1.462</v>
       </c>
       <c r="M23">
-        <v>0.188713098</v>
+        <v>0.197699436</v>
       </c>
       <c r="N23">
-        <v>-1.650713098</v>
+        <v>-1.659699436</v>
       </c>
       <c r="O23">
-        <v>-0.4952139294</v>
+        <v>-0.4979098308</v>
       </c>
       <c r="P23">
-        <v>-1.1554991686</v>
+        <v>-1.1617896052</v>
       </c>
       <c r="Q23">
-        <v>0.6245008314</v>
+        <v>0.6182103948</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1414327977959388</v>
+        <v>0.1426588593061432</v>
       </c>
       <c r="T23">
-        <v>2.208609648866948</v>
+        <v>2.236925157185755</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-2.324163000069025</v>
+        <v>-2.218519227338615</v>
       </c>
       <c r="W23">
-        <v>0.7838376354162762</v>
+        <v>0.7589268338064454</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3188,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-7.747210000230085</v>
+        <v>-7.395064091128717</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3196,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2782378136962097</v>
+        <v>0.2801378136962097</v>
       </c>
       <c r="C24">
-        <v>2.343086138806918</v>
+        <v>2.300829395202854</v>
       </c>
       <c r="D24">
-        <v>1.111506138806919</v>
+        <v>1.107359395202854</v>
       </c>
       <c r="E24">
-        <v>0.50742</v>
+        <v>0.5455300000000001</v>
       </c>
       <c r="F24">
-        <v>0.8384199999999999</v>
+        <v>0.87653</v>
       </c>
       <c r="G24">
         <v>2.07</v>
@@ -3232,37 +3243,37 @@
         <v>-1.462</v>
       </c>
       <c r="M24">
-        <v>0.197699436</v>
+        <v>0.206685774</v>
       </c>
       <c r="N24">
-        <v>-1.659699436</v>
+        <v>-1.668685774</v>
       </c>
       <c r="O24">
-        <v>-0.4979098308</v>
+        <v>-0.5006057322</v>
       </c>
       <c r="P24">
-        <v>-1.1617896052</v>
+        <v>-1.1680800418</v>
       </c>
       <c r="Q24">
-        <v>0.6182103948</v>
+        <v>0.6119199581999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1426588593061432</v>
+        <v>0.1439167665698594</v>
       </c>
       <c r="T24">
-        <v>2.236925157185755</v>
+        <v>2.265976133253103</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-2.218519227338615</v>
+        <v>-2.12206186962824</v>
       </c>
       <c r="W24">
-        <v>0.7589268338064454</v>
+        <v>0.7361821888583391</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3270,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-7.395064091128717</v>
+        <v>-7.073539565427469</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3278,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2801378136962097</v>
+        <v>0.2820378136962097</v>
       </c>
       <c r="C25">
-        <v>2.300829395202854</v>
+        <v>2.258603477463695</v>
       </c>
       <c r="D25">
-        <v>1.107359395202854</v>
+        <v>1.103243477463695</v>
       </c>
       <c r="E25">
-        <v>0.5455300000000001</v>
+        <v>0.5836399999999999</v>
       </c>
       <c r="F25">
-        <v>0.87653</v>
+        <v>0.91464</v>
       </c>
       <c r="G25">
         <v>2.07</v>
@@ -3314,37 +3325,37 @@
         <v>-1.462</v>
       </c>
       <c r="M25">
-        <v>0.206685774</v>
+        <v>0.215672112</v>
       </c>
       <c r="N25">
-        <v>-1.668685774</v>
+        <v>-1.677672112</v>
       </c>
       <c r="O25">
-        <v>-0.5006057322</v>
+        <v>-0.5033016336</v>
       </c>
       <c r="P25">
-        <v>-1.1680800418</v>
+        <v>-1.1743704784</v>
       </c>
       <c r="Q25">
-        <v>0.6119199581999999</v>
+        <v>0.6056295216000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1439167665698594</v>
+        <v>0.1452077766563049</v>
       </c>
       <c r="T25">
-        <v>2.265976133253103</v>
+        <v>2.295791608690644</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-2.12206186962824</v>
+        <v>-2.033642625060397</v>
       </c>
       <c r="W25">
-        <v>0.7361821888583391</v>
+        <v>0.7153329309892417</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3352,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-7.073539565427469</v>
+        <v>-6.778808750201324</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3360,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2820378136962097</v>
+        <v>0.2839378136962097</v>
       </c>
       <c r="C26">
-        <v>2.258603477463695</v>
+        <v>2.216408043134537</v>
       </c>
       <c r="D26">
-        <v>1.103243477463695</v>
+        <v>1.099158043134538</v>
       </c>
       <c r="E26">
-        <v>0.5836399999999999</v>
+        <v>0.62175</v>
       </c>
       <c r="F26">
-        <v>0.9146399999999999</v>
+        <v>0.95275</v>
       </c>
       <c r="G26">
         <v>2.07</v>
@@ -3396,37 +3407,37 @@
         <v>-1.462</v>
       </c>
       <c r="M26">
-        <v>0.215672112</v>
+        <v>0.22465845</v>
       </c>
       <c r="N26">
-        <v>-1.677672112</v>
+        <v>-1.68665845</v>
       </c>
       <c r="O26">
-        <v>-0.5033016336</v>
+        <v>-0.505997535</v>
       </c>
       <c r="P26">
-        <v>-1.1743704784</v>
+        <v>-1.180660915</v>
       </c>
       <c r="Q26">
-        <v>0.6056295216000001</v>
+        <v>0.5993390850000002</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1452077766563049</v>
+        <v>0.1465332136783889</v>
       </c>
       <c r="T26">
-        <v>2.295791608690644</v>
+        <v>2.326402163473185</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-2.033642625060397</v>
+        <v>-1.952296920057981</v>
       </c>
       <c r="W26">
-        <v>0.7153329309892417</v>
+        <v>0.6961516137496719</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3434,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-6.778808750201325</v>
+        <v>-6.50765640019327</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3442,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2839378136962097</v>
+        <v>0.2858378136962097</v>
       </c>
       <c r="C27">
-        <v>2.216408043134537</v>
+        <v>2.174242754814358</v>
       </c>
       <c r="D27">
-        <v>1.099158043134538</v>
+        <v>1.095102754814358</v>
       </c>
       <c r="E27">
-        <v>0.62175</v>
+        <v>0.6598600000000001</v>
       </c>
       <c r="F27">
-        <v>0.95275</v>
+        <v>0.9908600000000001</v>
       </c>
       <c r="G27">
         <v>2.07</v>
@@ -3478,37 +3489,37 @@
         <v>-1.462</v>
       </c>
       <c r="M27">
-        <v>0.22465845</v>
+        <v>0.233644788</v>
       </c>
       <c r="N27">
-        <v>-1.68665845</v>
+        <v>-1.695644788</v>
       </c>
       <c r="O27">
-        <v>-0.505997535</v>
+        <v>-0.5086934364</v>
       </c>
       <c r="P27">
-        <v>-1.180660915</v>
+        <v>-1.1869513516</v>
       </c>
       <c r="Q27">
-        <v>0.5993390850000002</v>
+        <v>0.5930486483999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1465332136783889</v>
+        <v>0.1478944733226915</v>
       </c>
       <c r="T27">
-        <v>2.326402163473185</v>
+        <v>2.357840030547147</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-1.952296920057981</v>
+        <v>-1.877208576978828</v>
       </c>
       <c r="W27">
-        <v>0.6961516137496719</v>
+        <v>0.6784457824516076</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3516,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-6.50765640019327</v>
+        <v>-6.25736192326276</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3524,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2858378136962097</v>
+        <v>0.2877378136962097</v>
       </c>
       <c r="C28">
-        <v>2.174242754814358</v>
+        <v>2.132107280063123</v>
       </c>
       <c r="D28">
-        <v>1.095102754814358</v>
+        <v>1.091077280063124</v>
       </c>
       <c r="E28">
-        <v>0.6598600000000001</v>
+        <v>0.6979700000000002</v>
       </c>
       <c r="F28">
-        <v>0.9908600000000001</v>
+        <v>1.02897</v>
       </c>
       <c r="G28">
         <v>2.07</v>
@@ -3560,37 +3571,37 @@
         <v>-1.462</v>
       </c>
       <c r="M28">
-        <v>0.233644788</v>
+        <v>0.2426311260000001</v>
       </c>
       <c r="N28">
-        <v>-1.695644788</v>
+        <v>-1.704631126</v>
       </c>
       <c r="O28">
-        <v>-0.5086934364</v>
+        <v>-0.5113893378</v>
       </c>
       <c r="P28">
-        <v>-1.1869513516</v>
+        <v>-1.1932417882</v>
       </c>
       <c r="Q28">
-        <v>0.5930486483999999</v>
+        <v>0.5867582118000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1478944733226915</v>
+        <v>0.1492930277517695</v>
       </c>
       <c r="T28">
-        <v>2.357840030547147</v>
+        <v>2.390139209047793</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-1.877208576978828</v>
+        <v>-1.807682333387019</v>
       </c>
       <c r="W28">
-        <v>0.6784457824516076</v>
+        <v>0.6620514942126592</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3598,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-6.25736192326276</v>
+        <v>-6.025607777956731</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3606,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2877378136962097</v>
+        <v>0.2896378136962097</v>
       </c>
       <c r="C29">
-        <v>2.132107280063123</v>
+        <v>2.090001291310951</v>
       </c>
       <c r="D29">
-        <v>1.091077280063124</v>
+        <v>1.087081291310952</v>
       </c>
       <c r="E29">
-        <v>0.6979700000000002</v>
+        <v>0.7360800000000001</v>
       </c>
       <c r="F29">
-        <v>1.02897</v>
+        <v>1.06708</v>
       </c>
       <c r="G29">
         <v>2.07</v>
@@ -3642,37 +3653,37 @@
         <v>-1.462</v>
       </c>
       <c r="M29">
-        <v>0.2426311260000001</v>
+        <v>0.251617464</v>
       </c>
       <c r="N29">
-        <v>-1.704631126</v>
+        <v>-1.713617464</v>
       </c>
       <c r="O29">
-        <v>-0.5113893378</v>
+        <v>-0.5140852391999999</v>
       </c>
       <c r="P29">
-        <v>-1.1932417882</v>
+        <v>-1.1995322248</v>
       </c>
       <c r="Q29">
-        <v>0.5867582118000001</v>
+        <v>0.5804677752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1492930277517695</v>
+        <v>0.1507304309149885</v>
       </c>
       <c r="T29">
-        <v>2.390139209047793</v>
+        <v>2.423335586951235</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-1.807682333387019</v>
+        <v>-1.743122250051769</v>
       </c>
       <c r="W29">
-        <v>0.6620514942126592</v>
+        <v>0.6468282265622072</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3680,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-6.025607777956731</v>
+        <v>-5.810407500172563</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3688,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2896378136962097</v>
+        <v>0.2915378136962097</v>
       </c>
       <c r="C30">
-        <v>2.090001291310951</v>
+        <v>2.047924465769246</v>
       </c>
       <c r="D30">
-        <v>1.087081291310952</v>
+        <v>1.083114465769246</v>
       </c>
       <c r="E30">
-        <v>0.7360800000000001</v>
+        <v>0.7741900000000002</v>
       </c>
       <c r="F30">
-        <v>1.06708</v>
+        <v>1.10519</v>
       </c>
       <c r="G30">
         <v>2.07</v>
@@ -3724,37 +3735,37 @@
         <v>-1.462</v>
       </c>
       <c r="M30">
-        <v>0.251617464</v>
+        <v>0.2606038020000001</v>
       </c>
       <c r="N30">
-        <v>-1.713617464</v>
+        <v>-1.722603802</v>
       </c>
       <c r="O30">
-        <v>-0.5140852391999999</v>
+        <v>-0.5167811406</v>
       </c>
       <c r="P30">
-        <v>-1.1995322248</v>
+        <v>-1.2058226614</v>
       </c>
       <c r="Q30">
-        <v>0.5804677752</v>
+        <v>0.5741773386</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1507304309149885</v>
+        <v>0.1522083243081573</v>
       </c>
       <c r="T30">
-        <v>2.423335586951235</v>
+        <v>2.457467074091393</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-1.743122250051769</v>
+        <v>-1.68301458625688</v>
       </c>
       <c r="W30">
-        <v>0.6468282265622072</v>
+        <v>0.6326548394393723</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3762,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-5.810407500172563</v>
+        <v>-5.610048620856268</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3770,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2915378136962097</v>
+        <v>0.2934378136962097</v>
       </c>
       <c r="C31">
-        <v>2.047924465769246</v>
+        <v>2.005876485343784</v>
       </c>
       <c r="D31">
-        <v>1.083114465769246</v>
+        <v>1.079176485343784</v>
       </c>
       <c r="E31">
-        <v>0.7741899999999999</v>
+        <v>0.8123</v>
       </c>
       <c r="F31">
-        <v>1.10519</v>
+        <v>1.1433</v>
       </c>
       <c r="G31">
         <v>2.07</v>
@@ -3806,37 +3817,37 @@
         <v>-1.462</v>
       </c>
       <c r="M31">
-        <v>0.260603802</v>
+        <v>0.26959014</v>
       </c>
       <c r="N31">
-        <v>-1.722603802</v>
+        <v>-1.73159014</v>
       </c>
       <c r="O31">
-        <v>-0.5167811406</v>
+        <v>-0.519477042</v>
       </c>
       <c r="P31">
-        <v>-1.2058226614</v>
+        <v>-1.212113098</v>
       </c>
       <c r="Q31">
-        <v>0.5741773386</v>
+        <v>0.5678869019999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1522083243081573</v>
+        <v>0.1537284432268453</v>
       </c>
       <c r="T31">
-        <v>2.457467074091393</v>
+        <v>2.492573746578413</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-1.683014586256881</v>
+        <v>-1.626914100048317</v>
       </c>
       <c r="W31">
-        <v>0.6326548394393724</v>
+        <v>0.6194263447913932</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3844,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-5.610048620856269</v>
+        <v>-5.423047000161058</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3852,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2934378136962097</v>
+        <v>0.2953378136962097</v>
       </c>
       <c r="C32">
-        <v>2.005876485343784</v>
+        <v>1.963857036549679</v>
       </c>
       <c r="D32">
-        <v>1.079176485343784</v>
+        <v>1.075267036549679</v>
       </c>
       <c r="E32">
-        <v>0.8123</v>
+        <v>0.8504100000000001</v>
       </c>
       <c r="F32">
-        <v>1.1433</v>
+        <v>1.18141</v>
       </c>
       <c r="G32">
         <v>2.07</v>
@@ -3888,37 +3899,37 @@
         <v>-1.462</v>
       </c>
       <c r="M32">
-        <v>0.26959014</v>
+        <v>0.278576478</v>
       </c>
       <c r="N32">
-        <v>-1.73159014</v>
+        <v>-1.740576478</v>
       </c>
       <c r="O32">
-        <v>-0.519477042</v>
+        <v>-0.5221729434</v>
       </c>
       <c r="P32">
-        <v>-1.212113098</v>
+        <v>-1.2184035346</v>
       </c>
       <c r="Q32">
-        <v>0.5678869019999999</v>
+        <v>0.5615964654000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1537284432268453</v>
+        <v>0.1552926235634662</v>
       </c>
       <c r="T32">
-        <v>2.492573746578413</v>
+        <v>2.528698003775201</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-1.626914100048317</v>
+        <v>-1.574433000046759</v>
       </c>
       <c r="W32">
-        <v>0.6194263447913932</v>
+        <v>0.6070513014110258</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3926,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-5.423047000161058</v>
+        <v>-5.248110000155863</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3934,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2953378136962097</v>
+        <v>0.2972378136962097</v>
       </c>
       <c r="C33">
-        <v>1.963857036549679</v>
+        <v>1.921865810428203</v>
       </c>
       <c r="D33">
-        <v>1.075267036549679</v>
+        <v>1.071385810428204</v>
       </c>
       <c r="E33">
-        <v>0.8504100000000001</v>
+        <v>0.88852</v>
       </c>
       <c r="F33">
-        <v>1.18141</v>
+        <v>1.21952</v>
       </c>
       <c r="G33">
         <v>2.07</v>
@@ -3970,37 +3981,37 @@
         <v>-1.462</v>
       </c>
       <c r="M33">
-        <v>0.278576478</v>
+        <v>0.287562816</v>
       </c>
       <c r="N33">
-        <v>-1.740576478</v>
+        <v>-1.749562816</v>
       </c>
       <c r="O33">
-        <v>-0.5221729434</v>
+        <v>-0.5248688448</v>
       </c>
       <c r="P33">
-        <v>-1.2184035346</v>
+        <v>-1.2246939712</v>
       </c>
       <c r="Q33">
-        <v>0.5615964654000001</v>
+        <v>0.5553060287999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1552926235634662</v>
+        <v>0.1569028092041055</v>
       </c>
       <c r="T33">
-        <v>2.528698003775201</v>
+        <v>2.565884739124837</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-1.574433000046759</v>
+        <v>-1.525231968795298</v>
       </c>
       <c r="W33">
-        <v>0.6070513014110258</v>
+        <v>0.5954496982419313</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4008,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-5.248110000155863</v>
+        <v>-5.084106562650994</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4016,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2972378136962097</v>
+        <v>0.2991378136962097</v>
       </c>
       <c r="C34">
-        <v>1.921865810428203</v>
+        <v>1.879902502465385</v>
       </c>
       <c r="D34">
-        <v>1.071385810428204</v>
+        <v>1.067532502465385</v>
       </c>
       <c r="E34">
-        <v>0.88852</v>
+        <v>0.9266300000000001</v>
       </c>
       <c r="F34">
-        <v>1.21952</v>
+        <v>1.25763</v>
       </c>
       <c r="G34">
         <v>2.07</v>
@@ -4052,37 +4063,37 @@
         <v>-1.462</v>
       </c>
       <c r="M34">
-        <v>0.287562816</v>
+        <v>0.296549154</v>
       </c>
       <c r="N34">
-        <v>-1.749562816</v>
+        <v>-1.758549154</v>
       </c>
       <c r="O34">
-        <v>-0.5248688448</v>
+        <v>-0.5275647461999999</v>
       </c>
       <c r="P34">
-        <v>-1.2246939712</v>
+        <v>-1.2309844078</v>
       </c>
       <c r="Q34">
-        <v>0.5553060287999998</v>
+        <v>0.5490155922</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1569028092041055</v>
+        <v>0.1585610600877488</v>
       </c>
       <c r="T34">
-        <v>2.565884739124837</v>
+        <v>2.604181526275954</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-1.525231968795298</v>
+        <v>-1.479012818225743</v>
       </c>
       <c r="W34">
-        <v>0.5954496982419313</v>
+        <v>0.5845512225376303</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4090,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-5.084106562650994</v>
+        <v>-4.930042727419144</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4098,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2991378136962097</v>
+        <v>0.3010378136962097</v>
       </c>
       <c r="C35">
-        <v>1.879902502465385</v>
+        <v>1.83796681251237</v>
       </c>
       <c r="D35">
-        <v>1.067532502465385</v>
+        <v>1.06370681251237</v>
       </c>
       <c r="E35">
-        <v>0.9266300000000001</v>
+        <v>0.9647400000000002</v>
       </c>
       <c r="F35">
-        <v>1.25763</v>
+        <v>1.29574</v>
       </c>
       <c r="G35">
         <v>2.07</v>
@@ -4134,37 +4145,37 @@
         <v>-1.462</v>
       </c>
       <c r="M35">
-        <v>0.296549154</v>
+        <v>0.305535492</v>
       </c>
       <c r="N35">
-        <v>-1.758549154</v>
+        <v>-1.767535492</v>
       </c>
       <c r="O35">
-        <v>-0.5275647461999999</v>
+        <v>-0.5302606475999999</v>
       </c>
       <c r="P35">
-        <v>-1.2309844078</v>
+        <v>-1.2372748444</v>
       </c>
       <c r="Q35">
-        <v>0.5490155922</v>
+        <v>0.5427251556000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1585610600877488</v>
+        <v>0.1602695609981692</v>
       </c>
       <c r="T35">
-        <v>2.604181526275954</v>
+        <v>2.64363882212862</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-1.479012818225743</v>
+        <v>-1.435512441219104</v>
       </c>
       <c r="W35">
-        <v>0.5845512225376303</v>
+        <v>0.5742938336394647</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4172,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-4.930042727419144</v>
+        <v>-4.785041470730346</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4180,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.3010378136962097</v>
+        <v>0.3029378136962096</v>
       </c>
       <c r="C36">
-        <v>1.83796681251237</v>
+        <v>1.796058444707484</v>
       </c>
       <c r="D36">
-        <v>1.06370681251237</v>
+        <v>1.059908444707485</v>
       </c>
       <c r="E36">
-        <v>0.9647400000000002</v>
+        <v>1.00285</v>
       </c>
       <c r="F36">
-        <v>1.29574</v>
+        <v>1.33385</v>
       </c>
       <c r="G36">
         <v>2.07</v>
@@ -4216,37 +4227,37 @@
         <v>-1.462</v>
       </c>
       <c r="M36">
-        <v>0.305535492</v>
+        <v>0.3145218300000001</v>
       </c>
       <c r="N36">
-        <v>-1.767535492</v>
+        <v>-1.77652183</v>
       </c>
       <c r="O36">
-        <v>-0.5302606475999999</v>
+        <v>-0.532956549</v>
       </c>
       <c r="P36">
-        <v>-1.2372748444</v>
+        <v>-1.243565281</v>
       </c>
       <c r="Q36">
-        <v>0.5427251556000001</v>
+        <v>0.5364347190000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1602695609981692</v>
+        <v>0.1620306311673718</v>
       </c>
       <c r="T36">
-        <v>2.64363882212862</v>
+        <v>2.684310188622906</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-1.435512441219104</v>
+        <v>-1.394497800041415</v>
       </c>
       <c r="W36">
-        <v>0.5742938336394647</v>
+        <v>0.5646225812497656</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4254,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-4.785041470730346</v>
+        <v>-4.64832600013805</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4262,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.3029378136962096</v>
+        <v>0.3048378136962097</v>
       </c>
       <c r="C37">
-        <v>1.796058444707484</v>
+        <v>1.754177107399963</v>
       </c>
       <c r="D37">
-        <v>1.059908444707485</v>
+        <v>1.056137107399963</v>
       </c>
       <c r="E37">
-        <v>1.00285</v>
+        <v>1.04096</v>
       </c>
       <c r="F37">
-        <v>1.33385</v>
+        <v>1.37196</v>
       </c>
       <c r="G37">
         <v>2.07</v>
@@ -4298,37 +4309,37 @@
         <v>-1.462</v>
       </c>
       <c r="M37">
-        <v>0.3145218300000001</v>
+        <v>0.323508168</v>
       </c>
       <c r="N37">
-        <v>-1.77652183</v>
+        <v>-1.785508168</v>
       </c>
       <c r="O37">
-        <v>-0.532956549</v>
+        <v>-0.5356524504</v>
       </c>
       <c r="P37">
-        <v>-1.243565281</v>
+        <v>-1.2498557176</v>
       </c>
       <c r="Q37">
-        <v>0.5364347190000001</v>
+        <v>0.5301442824</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1620306311673718</v>
+        <v>0.163846734779362</v>
       </c>
       <c r="T37">
-        <v>2.684310188622906</v>
+        <v>2.726252535320139</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-1.394497800041415</v>
+        <v>-1.355761750040265</v>
       </c>
       <c r="W37">
-        <v>0.5646225812497656</v>
+        <v>0.5554886206594944</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4336,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-4.64832600013805</v>
+        <v>-4.519205833467549</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4344,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.3048378136962097</v>
+        <v>0.3067378136962097</v>
       </c>
       <c r="C38">
-        <v>1.754177107399963</v>
+        <v>1.712322513075297</v>
       </c>
       <c r="D38">
-        <v>1.056137107399963</v>
+        <v>1.052392513075297</v>
       </c>
       <c r="E38">
-        <v>1.04096</v>
+        <v>1.07907</v>
       </c>
       <c r="F38">
-        <v>1.37196</v>
+        <v>1.41007</v>
       </c>
       <c r="G38">
         <v>2.07</v>
@@ -4380,37 +4391,37 @@
         <v>-1.462</v>
       </c>
       <c r="M38">
-        <v>0.323508168</v>
+        <v>0.332494506</v>
       </c>
       <c r="N38">
-        <v>-1.785508168</v>
+        <v>-1.794494506</v>
       </c>
       <c r="O38">
-        <v>-0.5356524504</v>
+        <v>-0.5383483518</v>
       </c>
       <c r="P38">
-        <v>-1.2498557176</v>
+        <v>-1.2561461542</v>
       </c>
       <c r="Q38">
-        <v>0.5301442824</v>
+        <v>0.5238538457999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.163846734779362</v>
+        <v>0.1657204924742725</v>
       </c>
       <c r="T38">
-        <v>2.726252535320139</v>
+        <v>2.769526385087125</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-1.355761750040265</v>
+        <v>-1.319119540579717</v>
       </c>
       <c r="W38">
-        <v>0.5554886206594944</v>
+        <v>0.5468483876686973</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4418,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-4.51920583346755</v>
+        <v>-4.397065135265724</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4426,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.3067378136962097</v>
+        <v>0.3086378136962097</v>
       </c>
       <c r="C39">
-        <v>1.712322513075297</v>
+        <v>1.670494378282168</v>
       </c>
       <c r="D39">
-        <v>1.052392513075297</v>
+        <v>1.048674378282168</v>
       </c>
       <c r="E39">
-        <v>1.07907</v>
+        <v>1.11718</v>
       </c>
       <c r="F39">
-        <v>1.41007</v>
+        <v>1.44818</v>
       </c>
       <c r="G39">
         <v>2.07</v>
@@ -4462,37 +4473,37 @@
         <v>-1.462</v>
       </c>
       <c r="M39">
-        <v>0.332494506</v>
+        <v>0.341480844</v>
       </c>
       <c r="N39">
-        <v>-1.794494506</v>
+        <v>-1.803480844</v>
       </c>
       <c r="O39">
-        <v>-0.5383483518</v>
+        <v>-0.5410442532</v>
       </c>
       <c r="P39">
-        <v>-1.2561461542</v>
+        <v>-1.2624365908</v>
       </c>
       <c r="Q39">
-        <v>0.5238538457999999</v>
+        <v>0.5175634091999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1657204924742725</v>
+        <v>0.1676546939657931</v>
       </c>
       <c r="T39">
-        <v>2.769526385087125</v>
+        <v>2.814196165491756</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-1.319119540579717</v>
+        <v>-1.284405868459198</v>
       </c>
       <c r="W39">
-        <v>0.5468483876686973</v>
+        <v>0.538662903782679</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4500,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-4.397065135265724</v>
+        <v>-4.281352894863995</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4508,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.3086378136962097</v>
+        <v>0.3105378136962097</v>
       </c>
       <c r="C40">
-        <v>1.670494378282168</v>
+        <v>1.628692423560924</v>
       </c>
       <c r="D40">
-        <v>1.048674378282168</v>
+        <v>1.044982423560924</v>
       </c>
       <c r="E40">
-        <v>1.11718</v>
+        <v>1.15529</v>
       </c>
       <c r="F40">
-        <v>1.44818</v>
+        <v>1.48629</v>
       </c>
       <c r="G40">
         <v>2.07</v>
@@ -4544,37 +4555,37 @@
         <v>-1.462</v>
       </c>
       <c r="M40">
-        <v>0.341480844</v>
+        <v>0.350467182</v>
       </c>
       <c r="N40">
-        <v>-1.803480844</v>
+        <v>-1.812467182</v>
       </c>
       <c r="O40">
-        <v>-0.5410442532</v>
+        <v>-0.5437401546</v>
       </c>
       <c r="P40">
-        <v>-1.2624365908</v>
+        <v>-1.2687270274</v>
       </c>
       <c r="Q40">
-        <v>0.5175634091999999</v>
+        <v>0.5112729726</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1676546939657931</v>
+        <v>0.1696523118996585</v>
       </c>
       <c r="T40">
-        <v>2.814196165491756</v>
+        <v>2.860330528860474</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-1.284405868459198</v>
+        <v>-1.251472384652552</v>
       </c>
       <c r="W40">
-        <v>0.538662903782679</v>
+        <v>0.5308971883010718</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4582,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-4.281352894863995</v>
+        <v>-4.171574615508507</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4590,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.3105378136962097</v>
+        <v>0.3124378136962097</v>
       </c>
       <c r="C41">
-        <v>1.628692423560924</v>
+        <v>1.58691637337356</v>
       </c>
       <c r="D41">
-        <v>1.044982423560924</v>
+        <v>1.04131637337356</v>
       </c>
       <c r="E41">
-        <v>1.15529</v>
+        <v>1.1934</v>
       </c>
       <c r="F41">
-        <v>1.48629</v>
+        <v>1.5244</v>
       </c>
       <c r="G41">
         <v>2.07</v>
@@ -4626,37 +4637,37 @@
         <v>-1.462</v>
       </c>
       <c r="M41">
-        <v>0.350467182</v>
+        <v>0.35945352</v>
       </c>
       <c r="N41">
-        <v>-1.812467182</v>
+        <v>-1.82145352</v>
       </c>
       <c r="O41">
-        <v>-0.5437401546</v>
+        <v>-0.546436056</v>
       </c>
       <c r="P41">
-        <v>-1.2687270274</v>
+        <v>-1.275017464</v>
       </c>
       <c r="Q41">
-        <v>0.5112729726</v>
+        <v>0.5049825360000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1696523118996585</v>
+        <v>0.1717165170979862</v>
       </c>
       <c r="T41">
-        <v>2.860330528860474</v>
+        <v>2.908002704341482</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-1.251472384652552</v>
+        <v>-1.220185575036238</v>
       </c>
       <c r="W41">
-        <v>0.5308971883010718</v>
+        <v>0.5235197585935449</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4664,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-4.171574615508507</v>
+        <v>-4.067285250120794</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4672,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.3124378136962097</v>
+        <v>0.3143378136962097</v>
       </c>
       <c r="C42">
-        <v>1.58691637337356</v>
+        <v>1.545165956035169</v>
       </c>
       <c r="D42">
-        <v>1.04131637337356</v>
+        <v>1.037675956035169</v>
       </c>
       <c r="E42">
-        <v>1.1934</v>
+        <v>1.23151</v>
       </c>
       <c r="F42">
-        <v>1.5244</v>
+        <v>1.56251</v>
       </c>
       <c r="G42">
         <v>2.07</v>
@@ -4708,37 +4719,37 @@
         <v>-1.462</v>
       </c>
       <c r="M42">
-        <v>0.35945352</v>
+        <v>0.368439858</v>
       </c>
       <c r="N42">
-        <v>-1.82145352</v>
+        <v>-1.830439858</v>
       </c>
       <c r="O42">
-        <v>-0.546436056</v>
+        <v>-0.5491319574</v>
       </c>
       <c r="P42">
-        <v>-1.275017464</v>
+        <v>-1.2813079006</v>
       </c>
       <c r="Q42">
-        <v>0.5049825360000002</v>
+        <v>0.4986920993999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1717165170979862</v>
+        <v>0.1738506953538843</v>
       </c>
       <c r="T42">
-        <v>2.908002704341482</v>
+        <v>2.957290885770998</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-1.220185575036238</v>
+        <v>-1.190424951254867</v>
       </c>
       <c r="W42">
-        <v>0.5235197585935449</v>
+        <v>0.5165022035058976</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4746,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-4.067285250120794</v>
+        <v>-3.968083170849556</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4754,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.3143378136962097</v>
+        <v>0.3162378136962097</v>
       </c>
       <c r="C43">
-        <v>1.545165956035169</v>
+        <v>1.503440903646822</v>
       </c>
       <c r="D43">
-        <v>1.037675956035169</v>
+        <v>1.034060903646822</v>
       </c>
       <c r="E43">
-        <v>1.23151</v>
+        <v>1.26962</v>
       </c>
       <c r="F43">
-        <v>1.56251</v>
+        <v>1.60062</v>
       </c>
       <c r="G43">
         <v>2.07</v>
@@ -4790,37 +4801,37 @@
         <v>-1.462</v>
       </c>
       <c r="M43">
-        <v>0.368439858</v>
+        <v>0.377426196</v>
       </c>
       <c r="N43">
-        <v>-1.830439858</v>
+        <v>-1.839426196</v>
       </c>
       <c r="O43">
-        <v>-0.5491319574</v>
+        <v>-0.5518278588</v>
       </c>
       <c r="P43">
-        <v>-1.2813079006</v>
+        <v>-1.2875983372</v>
       </c>
       <c r="Q43">
-        <v>0.4986920993999999</v>
+        <v>0.4924016628000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1738506953538843</v>
+        <v>0.176058465963434</v>
       </c>
       <c r="T43">
-        <v>2.957290885770998</v>
+        <v>3.008278659663602</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-1.190424951254867</v>
+        <v>-1.162081500034512</v>
       </c>
       <c r="W43">
-        <v>0.5165022035058976</v>
+        <v>0.509818817708138</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4828,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-3.968083170849556</v>
+        <v>-3.873605000115042</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4836,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.3162378136962097</v>
+        <v>0.3181378136962097</v>
       </c>
       <c r="C44">
-        <v>1.503440903646822</v>
+        <v>1.461740952029854</v>
       </c>
       <c r="D44">
-        <v>1.034060903646822</v>
+        <v>1.030470952029854</v>
       </c>
       <c r="E44">
-        <v>1.26962</v>
+        <v>1.30773</v>
       </c>
       <c r="F44">
-        <v>1.60062</v>
+        <v>1.63873</v>
       </c>
       <c r="G44">
         <v>2.07</v>
@@ -4872,37 +4883,37 @@
         <v>-1.462</v>
       </c>
       <c r="M44">
-        <v>0.377426196</v>
+        <v>0.386412534</v>
       </c>
       <c r="N44">
-        <v>-1.839426196</v>
+        <v>-1.848412534</v>
       </c>
       <c r="O44">
-        <v>-0.5518278588</v>
+        <v>-0.5545237601999999</v>
       </c>
       <c r="P44">
-        <v>-1.2875983372</v>
+        <v>-1.2938887738</v>
       </c>
       <c r="Q44">
-        <v>0.4924016628000001</v>
+        <v>0.4861112262</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.176058465963434</v>
+        <v>0.1783437022084065</v>
       </c>
       <c r="T44">
-        <v>3.008278659663602</v>
+        <v>3.061055478254191</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-1.162081500034513</v>
+        <v>-1.135056348870919</v>
       </c>
       <c r="W44">
-        <v>0.5098188177081381</v>
+        <v>0.5034462870637628</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4910,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-3.873605000115043</v>
+        <v>-3.783521162903064</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4918,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.3181378136962097</v>
+        <v>0.3200378136962097</v>
       </c>
       <c r="C45">
-        <v>1.461740952029854</v>
+        <v>1.420065840661505</v>
       </c>
       <c r="D45">
-        <v>1.030470952029854</v>
+        <v>1.026905840661504</v>
       </c>
       <c r="E45">
-        <v>1.30773</v>
+        <v>1.34584</v>
       </c>
       <c r="F45">
-        <v>1.63873</v>
+        <v>1.67684</v>
       </c>
       <c r="G45">
         <v>2.07</v>
@@ -4954,37 +4965,37 @@
         <v>-1.462</v>
       </c>
       <c r="M45">
-        <v>0.386412534</v>
+        <v>0.395398872</v>
       </c>
       <c r="N45">
-        <v>-1.848412534</v>
+        <v>-1.857398872</v>
       </c>
       <c r="O45">
-        <v>-0.5545237601999999</v>
+        <v>-0.5572196616</v>
       </c>
       <c r="P45">
-        <v>-1.2938887738</v>
+        <v>-1.3001792104</v>
       </c>
       <c r="Q45">
-        <v>0.4861112262</v>
+        <v>0.4798207896</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1783437022084065</v>
+        <v>0.1807105540335566</v>
       </c>
       <c r="T45">
-        <v>3.061055478254191</v>
+        <v>3.115717183223016</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-1.135056348870919</v>
+        <v>-1.109259613669307</v>
       </c>
       <c r="W45">
-        <v>0.5034462870637628</v>
+        <v>0.4973634169032227</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4992,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-3.783521162903064</v>
+        <v>-3.697532045564358</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5000,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.3200378136962097</v>
+        <v>0.3219378136962097</v>
       </c>
       <c r="C46">
-        <v>1.420065840661505</v>
+        <v>1.378415312611898</v>
       </c>
       <c r="D46">
-        <v>1.026905840661504</v>
+        <v>1.023365312611898</v>
       </c>
       <c r="E46">
-        <v>1.34584</v>
+        <v>1.38395</v>
       </c>
       <c r="F46">
-        <v>1.67684</v>
+        <v>1.71495</v>
       </c>
       <c r="G46">
         <v>2.07</v>
@@ -5036,37 +5047,37 @@
         <v>-1.462</v>
       </c>
       <c r="M46">
-        <v>0.395398872</v>
+        <v>0.40438521</v>
       </c>
       <c r="N46">
-        <v>-1.857398872</v>
+        <v>-1.86638521</v>
       </c>
       <c r="O46">
-        <v>-0.5572196616</v>
+        <v>-0.559915563</v>
       </c>
       <c r="P46">
-        <v>-1.3001792104</v>
+        <v>-1.306469647</v>
       </c>
       <c r="Q46">
-        <v>0.4798207896</v>
+        <v>0.4735303529999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1807105540335566</v>
+        <v>0.1831634731978031</v>
       </c>
       <c r="T46">
-        <v>3.115717183223016</v>
+        <v>3.172366586554343</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-1.109259613669307</v>
+        <v>-1.084609400032212</v>
       </c>
       <c r="W46">
-        <v>0.4973634169032227</v>
+        <v>0.4915508965275955</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5074,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-3.697532045564358</v>
+        <v>-3.61536466677404</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5082,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.3219378136962097</v>
+        <v>0.3238378136962097</v>
       </c>
       <c r="C47">
-        <v>1.378415312611898</v>
+        <v>1.336789114482314</v>
       </c>
       <c r="D47">
-        <v>1.023365312611898</v>
+        <v>1.019849114482315</v>
       </c>
       <c r="E47">
-        <v>1.38395</v>
+        <v>1.42206</v>
       </c>
       <c r="F47">
-        <v>1.71495</v>
+        <v>1.75306</v>
       </c>
       <c r="G47">
         <v>2.07</v>
@@ -5118,37 +5129,37 @@
         <v>-1.462</v>
       </c>
       <c r="M47">
-        <v>0.40438521</v>
+        <v>0.413371548</v>
       </c>
       <c r="N47">
-        <v>-1.86638521</v>
+        <v>-1.875371548</v>
       </c>
       <c r="O47">
-        <v>-0.559915563</v>
+        <v>-0.5626114644</v>
       </c>
       <c r="P47">
-        <v>-1.306469647</v>
+        <v>-1.3127600836</v>
       </c>
       <c r="Q47">
-        <v>0.4735303529999999</v>
+        <v>0.4672399164000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1831634731978031</v>
+        <v>0.1857072412199846</v>
       </c>
       <c r="T47">
-        <v>3.172366586554343</v>
+        <v>3.23111411593498</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-1.084609400032212</v>
+        <v>-1.06103093481412</v>
       </c>
       <c r="W47">
-        <v>0.4915508965275955</v>
+        <v>0.4859910944291695</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5156,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-3.61536466677404</v>
+        <v>-3.536769782713733</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5164,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.3238378136962097</v>
+        <v>0.3257378136962097</v>
       </c>
       <c r="C48">
-        <v>1.336789114482314</v>
+        <v>1.295186996344741</v>
       </c>
       <c r="D48">
-        <v>1.019849114482315</v>
+        <v>1.016356996344741</v>
       </c>
       <c r="E48">
-        <v>1.42206</v>
+        <v>1.46017</v>
       </c>
       <c r="F48">
-        <v>1.75306</v>
+        <v>1.79117</v>
       </c>
       <c r="G48">
         <v>2.07</v>
@@ -5200,37 +5211,37 @@
         <v>-1.462</v>
       </c>
       <c r="M48">
-        <v>0.413371548</v>
+        <v>0.4223578860000001</v>
       </c>
       <c r="N48">
-        <v>-1.875371548</v>
+        <v>-1.884357886</v>
       </c>
       <c r="O48">
-        <v>-0.5626114644</v>
+        <v>-0.5653073658</v>
       </c>
       <c r="P48">
-        <v>-1.3127600836</v>
+        <v>-1.3190505202</v>
       </c>
       <c r="Q48">
-        <v>0.4672399164000001</v>
+        <v>0.4609494797999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1857072412199846</v>
+        <v>0.1883470004882862</v>
       </c>
       <c r="T48">
-        <v>3.23111411593498</v>
+        <v>3.292078533216772</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-1.06103093481412</v>
+        <v>-1.038455808541479</v>
       </c>
       <c r="W48">
-        <v>0.4859910944291695</v>
+        <v>0.4806678796540808</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5238,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-3.536769782713733</v>
+        <v>-3.461519361804931</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5246,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.3257378136962097</v>
+        <v>0.3276378136962097</v>
       </c>
       <c r="C49">
-        <v>1.295186996344741</v>
+        <v>1.253608711682645</v>
       </c>
       <c r="D49">
-        <v>1.016356996344741</v>
+        <v>1.012888711682645</v>
       </c>
       <c r="E49">
-        <v>1.46017</v>
+        <v>1.49828</v>
       </c>
       <c r="F49">
-        <v>1.79117</v>
+        <v>1.82928</v>
       </c>
       <c r="G49">
         <v>2.07</v>
@@ -5282,37 +5293,37 @@
         <v>-1.462</v>
       </c>
       <c r="M49">
-        <v>0.4223578860000001</v>
+        <v>0.431344224</v>
       </c>
       <c r="N49">
-        <v>-1.884357886</v>
+        <v>-1.893344224</v>
       </c>
       <c r="O49">
-        <v>-0.5653073658</v>
+        <v>-0.5680032671999999</v>
       </c>
       <c r="P49">
-        <v>-1.3190505202</v>
+        <v>-1.3253409568</v>
       </c>
       <c r="Q49">
-        <v>0.4609494797999998</v>
+        <v>0.4546590431999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1883470004882862</v>
+        <v>0.1910882889592148</v>
       </c>
       <c r="T49">
-        <v>3.292078533216772</v>
+        <v>3.355387735778632</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-1.038455808541479</v>
+        <v>-1.016821312530199</v>
       </c>
       <c r="W49">
-        <v>0.4806678796540808</v>
+        <v>0.4755664654946208</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5320,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-3.461519361804931</v>
+        <v>-3.389404375100662</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5328,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3276378136962096</v>
+        <v>0.3295378136962097</v>
       </c>
       <c r="C50">
-        <v>1.253608711682646</v>
+        <v>1.212054017332972</v>
       </c>
       <c r="D50">
-        <v>1.012888711682645</v>
+        <v>1.009444017332972</v>
       </c>
       <c r="E50">
-        <v>1.49828</v>
+        <v>1.53639</v>
       </c>
       <c r="F50">
-        <v>1.82928</v>
+        <v>1.86739</v>
       </c>
       <c r="G50">
         <v>2.07</v>
@@ -5364,37 +5375,37 @@
         <v>-1.462</v>
       </c>
       <c r="M50">
-        <v>0.4313442239999999</v>
+        <v>0.440330562</v>
       </c>
       <c r="N50">
-        <v>-1.893344224</v>
+        <v>-1.902330562</v>
       </c>
       <c r="O50">
-        <v>-0.5680032671999999</v>
+        <v>-0.5706991685999999</v>
       </c>
       <c r="P50">
-        <v>-1.3253409568</v>
+        <v>-1.3316313934</v>
       </c>
       <c r="Q50">
-        <v>0.4546590432000002</v>
+        <v>0.4483686066000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1910882889592148</v>
+        <v>0.1939370789388073</v>
       </c>
       <c r="T50">
-        <v>3.355387735778632</v>
+        <v>3.421179652166449</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-1.016821312530199</v>
+        <v>-0.9960698571724393</v>
       </c>
       <c r="W50">
-        <v>0.4755664654946208</v>
+        <v>0.4706732723212612</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5402,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-3.389404375100662</v>
+        <v>-3.320232857241465</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5410,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3295378136962097</v>
+        <v>0.3314378136962097</v>
       </c>
       <c r="C51">
-        <v>1.212054017332972</v>
+        <v>1.170522673429308</v>
       </c>
       <c r="D51">
-        <v>1.009444017332972</v>
+        <v>1.006022673429308</v>
       </c>
       <c r="E51">
-        <v>1.53639</v>
+        <v>1.5745</v>
       </c>
       <c r="F51">
-        <v>1.86739</v>
+        <v>1.9055</v>
       </c>
       <c r="G51">
         <v>2.07</v>
@@ -5446,37 +5457,37 @@
         <v>-1.462</v>
       </c>
       <c r="M51">
-        <v>0.440330562</v>
+        <v>0.4493169</v>
       </c>
       <c r="N51">
-        <v>-1.902330562</v>
+        <v>-1.9113169</v>
       </c>
       <c r="O51">
-        <v>-0.5706991685999999</v>
+        <v>-0.57339507</v>
       </c>
       <c r="P51">
-        <v>-1.3316313934</v>
+        <v>-1.33792183</v>
       </c>
       <c r="Q51">
-        <v>0.4483686066000001</v>
+        <v>0.44207817</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1939370789388073</v>
+        <v>0.1968998205175834</v>
       </c>
       <c r="T51">
-        <v>3.421179652166449</v>
+        <v>3.489603245209778</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.9960698571724393</v>
+        <v>-0.9761484600289905</v>
       </c>
       <c r="W51">
-        <v>0.4706732723212612</v>
+        <v>0.465975806874836</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5484,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-3.320232857241465</v>
+        <v>-3.253828200096636</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5492,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3314378136962097</v>
+        <v>0.3333378136962097</v>
       </c>
       <c r="C52">
-        <v>1.170522673429308</v>
+        <v>1.129014443346207</v>
       </c>
       <c r="D52">
-        <v>1.006022673429308</v>
+        <v>1.002624443346207</v>
       </c>
       <c r="E52">
-        <v>1.5745</v>
+        <v>1.61261</v>
       </c>
       <c r="F52">
-        <v>1.9055</v>
+        <v>1.94361</v>
       </c>
       <c r="G52">
         <v>2.07</v>
@@ -5528,37 +5539,37 @@
         <v>-1.462</v>
       </c>
       <c r="M52">
-        <v>0.4493169</v>
+        <v>0.4583032380000001</v>
       </c>
       <c r="N52">
-        <v>-1.9113169</v>
+        <v>-1.920303238</v>
       </c>
       <c r="O52">
-        <v>-0.57339507</v>
+        <v>-0.5760909714</v>
       </c>
       <c r="P52">
-        <v>-1.33792183</v>
+        <v>-1.3442122666</v>
       </c>
       <c r="Q52">
-        <v>0.44207817</v>
+        <v>0.4357877334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1968998205175834</v>
+        <v>0.1999834903240647</v>
       </c>
       <c r="T52">
-        <v>3.489603245209778</v>
+        <v>3.560819637969161</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.9761484600289905</v>
+        <v>-0.9570082941460691</v>
       </c>
       <c r="W52">
-        <v>0.465975806874836</v>
+        <v>0.4614625557596431</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5566,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-3.253828200096636</v>
+        <v>-3.190027647153564</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5574,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3333378136962097</v>
+        <v>0.3352378136962097</v>
       </c>
       <c r="C53">
-        <v>1.129014443346207</v>
+        <v>1.087529093644635</v>
       </c>
       <c r="D53">
-        <v>1.002624443346207</v>
+        <v>0.999249093644635</v>
       </c>
       <c r="E53">
-        <v>1.61261</v>
+        <v>1.65072</v>
       </c>
       <c r="F53">
-        <v>1.94361</v>
+        <v>1.98172</v>
       </c>
       <c r="G53">
         <v>2.07</v>
@@ -5610,37 +5621,37 @@
         <v>-1.462</v>
       </c>
       <c r="M53">
-        <v>0.4583032380000001</v>
+        <v>0.467289576</v>
       </c>
       <c r="N53">
-        <v>-1.920303238</v>
+        <v>-1.929289576</v>
       </c>
       <c r="O53">
-        <v>-0.5760909714</v>
+        <v>-0.5787868728</v>
       </c>
       <c r="P53">
-        <v>-1.3442122666</v>
+        <v>-1.3505027032</v>
       </c>
       <c r="Q53">
-        <v>0.4357877334</v>
+        <v>0.4294972967999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1999834903240647</v>
+        <v>0.2031956463724827</v>
       </c>
       <c r="T53">
-        <v>3.560819637969161</v>
+        <v>3.635003380426852</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.9570082941460691</v>
+        <v>-0.9386042884894139</v>
       </c>
       <c r="W53">
-        <v>0.4614625557596431</v>
+        <v>0.4571228912258038</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5648,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-3.190027647153564</v>
+        <v>-3.12868096163138</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5656,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3352378136962097</v>
+        <v>0.3371378136962097</v>
       </c>
       <c r="C54">
-        <v>1.087529093644635</v>
+        <v>1.046066394018513</v>
       </c>
       <c r="D54">
-        <v>0.999249093644635</v>
+        <v>0.9958963940185133</v>
       </c>
       <c r="E54">
-        <v>1.65072</v>
+        <v>1.68883</v>
       </c>
       <c r="F54">
-        <v>1.98172</v>
+        <v>2.01983</v>
       </c>
       <c r="G54">
         <v>2.07</v>
@@ -5692,37 +5703,37 @@
         <v>-1.462</v>
       </c>
       <c r="M54">
-        <v>0.467289576</v>
+        <v>0.4762759140000001</v>
       </c>
       <c r="N54">
-        <v>-1.929289576</v>
+        <v>-1.938275914</v>
       </c>
       <c r="O54">
-        <v>-0.5787868728</v>
+        <v>-0.5814827742000001</v>
       </c>
       <c r="P54">
-        <v>-1.3505027032</v>
+        <v>-1.3567931398</v>
       </c>
       <c r="Q54">
-        <v>0.4294972967999999</v>
+        <v>0.4232068601999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2031956463724827</v>
+        <v>0.2065444899123228</v>
       </c>
       <c r="T54">
-        <v>3.635003380426852</v>
+        <v>3.712343877882743</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.9386042884894139</v>
+        <v>-0.9208947736122552</v>
       </c>
       <c r="W54">
-        <v>0.4571228912258038</v>
+        <v>0.4529469876177698</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5730,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-3.12868096163138</v>
+        <v>-3.069649245374184</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5738,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3371378136962097</v>
+        <v>0.3390378136962097</v>
       </c>
       <c r="C55">
-        <v>1.046066394018513</v>
+        <v>1.004626117242338</v>
       </c>
       <c r="D55">
-        <v>0.9958963940185133</v>
+        <v>0.9925661172423379</v>
       </c>
       <c r="E55">
-        <v>1.68883</v>
+        <v>1.72694</v>
       </c>
       <c r="F55">
-        <v>2.01983</v>
+        <v>2.05794</v>
       </c>
       <c r="G55">
         <v>2.07</v>
@@ -5774,37 +5785,37 @@
         <v>-1.462</v>
       </c>
       <c r="M55">
-        <v>0.4762759140000001</v>
+        <v>0.4852622520000001</v>
       </c>
       <c r="N55">
-        <v>-1.938275914</v>
+        <v>-1.947262252</v>
       </c>
       <c r="O55">
-        <v>-0.5814827742000001</v>
+        <v>-0.5841786756</v>
       </c>
       <c r="P55">
-        <v>-1.3567931398</v>
+        <v>-1.3630835764</v>
       </c>
       <c r="Q55">
-        <v>0.4232068601999999</v>
+        <v>0.4169164236</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2065444899123228</v>
+        <v>0.2100389353451994</v>
       </c>
       <c r="T55">
-        <v>3.712343877882743</v>
+        <v>3.793047005662802</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.9208947736122552</v>
+        <v>-0.9038411666935096</v>
       </c>
       <c r="W55">
-        <v>0.4529469876177698</v>
+        <v>0.4489257471063296</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5812,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-3.069649245374184</v>
+        <v>-3.012803888978365</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5820,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3390378136962097</v>
+        <v>0.3409378136962097</v>
       </c>
       <c r="C56">
-        <v>1.004626117242338</v>
+        <v>0.963208039119841</v>
       </c>
       <c r="D56">
-        <v>0.9925661172423379</v>
+        <v>0.9892580391198411</v>
       </c>
       <c r="E56">
-        <v>1.72694</v>
+        <v>1.76505</v>
       </c>
       <c r="F56">
-        <v>2.05794</v>
+        <v>2.09605</v>
       </c>
       <c r="G56">
         <v>2.07</v>
@@ -5856,37 +5867,37 @@
         <v>-1.462</v>
       </c>
       <c r="M56">
-        <v>0.4852622520000001</v>
+        <v>0.49424859</v>
       </c>
       <c r="N56">
-        <v>-1.947262252</v>
+        <v>-1.95624859</v>
       </c>
       <c r="O56">
-        <v>-0.5841786756</v>
+        <v>-0.586874577</v>
       </c>
       <c r="P56">
-        <v>-1.3630835764</v>
+        <v>-1.369374013</v>
       </c>
       <c r="Q56">
-        <v>0.4169164236</v>
+        <v>0.4106259870000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2100389353451994</v>
+        <v>0.2136886894639816</v>
       </c>
       <c r="T56">
-        <v>3.793047005662802</v>
+        <v>3.877336939121976</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.9038411666935096</v>
+        <v>-0.887407690935446</v>
       </c>
       <c r="W56">
-        <v>0.4489257471063296</v>
+        <v>0.4450507335225782</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5894,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-3.012803888978365</v>
+        <v>-2.958025636451487</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5902,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3409378136962097</v>
+        <v>0.3428378136962097</v>
       </c>
       <c r="C57">
-        <v>0.963208039119841</v>
+        <v>0.9218119384336823</v>
       </c>
       <c r="D57">
-        <v>0.9892580391198411</v>
+        <v>0.9859719384336822</v>
       </c>
       <c r="E57">
-        <v>1.76505</v>
+        <v>1.80316</v>
       </c>
       <c r="F57">
-        <v>2.09605</v>
+        <v>2.13416</v>
       </c>
       <c r="G57">
         <v>2.07</v>
@@ -5938,37 +5949,37 @@
         <v>-1.462</v>
       </c>
       <c r="M57">
-        <v>0.49424859</v>
+        <v>0.503234928</v>
       </c>
       <c r="N57">
-        <v>-1.95624859</v>
+        <v>-1.965234928</v>
       </c>
       <c r="O57">
-        <v>-0.586874577</v>
+        <v>-0.5895704784</v>
       </c>
       <c r="P57">
-        <v>-1.369374013</v>
+        <v>-1.3756644496</v>
       </c>
       <c r="Q57">
-        <v>0.4106259870000002</v>
+        <v>0.4043355503999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2136886894639816</v>
+        <v>0.2175043414972539</v>
       </c>
       <c r="T57">
-        <v>3.877336939121976</v>
+        <v>3.96545823319293</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.887407690935446</v>
+        <v>-0.8715611250258845</v>
       </c>
       <c r="W57">
-        <v>0.4450507335225782</v>
+        <v>0.4413141132811036</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5976,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-2.958025636451487</v>
+        <v>-2.905203750086282</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5984,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3428378136962097</v>
+        <v>0.3447378136962097</v>
       </c>
       <c r="C58">
-        <v>0.9218119384336823</v>
+        <v>0.8804375968961327</v>
       </c>
       <c r="D58">
-        <v>0.9859719384336822</v>
+        <v>0.9827075968961329</v>
       </c>
       <c r="E58">
-        <v>1.80316</v>
+        <v>1.84127</v>
       </c>
       <c r="F58">
-        <v>2.13416</v>
+        <v>2.17227</v>
       </c>
       <c r="G58">
         <v>2.07</v>
@@ -6020,37 +6031,37 @@
         <v>-1.462</v>
       </c>
       <c r="M58">
-        <v>0.503234928</v>
+        <v>0.5122212660000001</v>
       </c>
       <c r="N58">
-        <v>-1.965234928</v>
+        <v>-1.974221266</v>
       </c>
       <c r="O58">
-        <v>-0.5895704784</v>
+        <v>-0.5922663798</v>
       </c>
       <c r="P58">
-        <v>-1.3756644496</v>
+        <v>-1.3819548862</v>
       </c>
       <c r="Q58">
-        <v>0.4043355503999999</v>
+        <v>0.3980451138000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2175043414972539</v>
+        <v>0.2214974657181203</v>
       </c>
       <c r="T58">
-        <v>3.96545823319293</v>
+        <v>4.057678192104394</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.8715611250258845</v>
+        <v>-0.8562705789727987</v>
       </c>
       <c r="W58">
-        <v>0.4413141132811036</v>
+        <v>0.4377086025217859</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6058,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-2.905203750086282</v>
+        <v>-2.854235263242662</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6066,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3447378136962097</v>
+        <v>0.3466378136962097</v>
       </c>
       <c r="C59">
-        <v>0.8804375968961327</v>
+        <v>0.8390847991007395</v>
       </c>
       <c r="D59">
-        <v>0.9827075968961329</v>
+        <v>0.9794647991007397</v>
       </c>
       <c r="E59">
-        <v>1.84127</v>
+        <v>1.87938</v>
       </c>
       <c r="F59">
-        <v>2.17227</v>
+        <v>2.21038</v>
       </c>
       <c r="G59">
         <v>2.07</v>
@@ -6102,37 +6113,37 @@
         <v>-1.462</v>
       </c>
       <c r="M59">
-        <v>0.5122212660000001</v>
+        <v>0.5212076040000001</v>
       </c>
       <c r="N59">
-        <v>-1.974221266</v>
+        <v>-1.983207604</v>
       </c>
       <c r="O59">
-        <v>-0.5922663798</v>
+        <v>-0.5949622811999999</v>
       </c>
       <c r="P59">
-        <v>-1.3819548862</v>
+        <v>-1.3882453228</v>
       </c>
       <c r="Q59">
-        <v>0.3980451138000001</v>
+        <v>0.3917546772</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2214974657181203</v>
+        <v>0.2256807387114088</v>
       </c>
       <c r="T59">
-        <v>4.057678192104394</v>
+        <v>4.154289577630689</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.8562705789727987</v>
+        <v>-0.84150729312844</v>
       </c>
       <c r="W59">
-        <v>0.4377086025217859</v>
+        <v>0.4342274197196861</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6140,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-2.854235263242662</v>
+        <v>-2.805024310428133</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6148,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3466378136962097</v>
+        <v>0.3485378136962097</v>
       </c>
       <c r="C60">
-        <v>0.83908479910074</v>
+        <v>0.7977533324749437</v>
       </c>
       <c r="D60">
-        <v>0.9794647991007397</v>
+        <v>0.9762433324749437</v>
       </c>
       <c r="E60">
-        <v>1.87938</v>
+        <v>1.91749</v>
       </c>
       <c r="F60">
-        <v>2.21038</v>
+        <v>2.24849</v>
       </c>
       <c r="G60">
         <v>2.07</v>
@@ -6184,37 +6195,37 @@
         <v>-1.462</v>
       </c>
       <c r="M60">
-        <v>0.521207604</v>
+        <v>0.530193942</v>
       </c>
       <c r="N60">
-        <v>-1.983207604</v>
+        <v>-1.992193942</v>
       </c>
       <c r="O60">
-        <v>-0.5949622811999999</v>
+        <v>-0.5976581826</v>
       </c>
       <c r="P60">
-        <v>-1.3882453228</v>
+        <v>-1.3945357594</v>
       </c>
       <c r="Q60">
-        <v>0.3917546772</v>
+        <v>0.3854642406</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2256807387114088</v>
+        <v>0.230068073801931</v>
       </c>
       <c r="T60">
-        <v>4.154289577630688</v>
+        <v>4.255613713670461</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.8415072931284403</v>
+        <v>-0.827244457651687</v>
       </c>
       <c r="W60">
-        <v>0.4342274197196862</v>
+        <v>0.4308642431142679</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6222,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-2.805024310428134</v>
+        <v>-2.757481525505623</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6230,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3485378136962097</v>
+        <v>0.3504378136962097</v>
       </c>
       <c r="C61">
-        <v>0.7977533324749437</v>
+        <v>0.756442987233628</v>
       </c>
       <c r="D61">
-        <v>0.9762433324749437</v>
+        <v>0.9730429872336284</v>
       </c>
       <c r="E61">
-        <v>1.91749</v>
+        <v>1.9556</v>
       </c>
       <c r="F61">
-        <v>2.24849</v>
+        <v>2.2866</v>
       </c>
       <c r="G61">
         <v>2.07</v>
@@ -6266,37 +6277,37 @@
         <v>-1.462</v>
       </c>
       <c r="M61">
-        <v>0.530193942</v>
+        <v>0.5391802800000001</v>
       </c>
       <c r="N61">
-        <v>-1.992193942</v>
+        <v>-2.00118028</v>
       </c>
       <c r="O61">
-        <v>-0.5976581826</v>
+        <v>-0.6003540839999999</v>
       </c>
       <c r="P61">
-        <v>-1.3945357594</v>
+        <v>-1.400826196</v>
       </c>
       <c r="Q61">
-        <v>0.3854642406</v>
+        <v>0.3791738040000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.230068073801931</v>
+        <v>0.2346747756469792</v>
       </c>
       <c r="T61">
-        <v>4.255613713670461</v>
+        <v>4.362004056512221</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.827244457651687</v>
+        <v>-0.8134570500241587</v>
       </c>
       <c r="W61">
-        <v>0.4308642431142679</v>
+        <v>0.4276131723956966</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6304,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-2.757481525505623</v>
+        <v>-2.711523500080529</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6312,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3504378136962097</v>
+        <v>0.3523378136962097</v>
       </c>
       <c r="C62">
-        <v>0.756442987233628</v>
+        <v>0.7151535563335796</v>
       </c>
       <c r="D62">
-        <v>0.9730429872336284</v>
+        <v>0.9698635563335797</v>
       </c>
       <c r="E62">
-        <v>1.9556</v>
+        <v>1.99371</v>
       </c>
       <c r="F62">
-        <v>2.2866</v>
+        <v>2.32471</v>
       </c>
       <c r="G62">
         <v>2.07</v>
@@ -6348,37 +6359,37 @@
         <v>-1.462</v>
       </c>
       <c r="M62">
-        <v>0.5391802800000001</v>
+        <v>0.548166618</v>
       </c>
       <c r="N62">
-        <v>-2.00118028</v>
+        <v>-2.010166618</v>
       </c>
       <c r="O62">
-        <v>-0.6003540839999999</v>
+        <v>-0.6030499854</v>
       </c>
       <c r="P62">
-        <v>-1.400826196</v>
+        <v>-1.4071166326</v>
       </c>
       <c r="Q62">
-        <v>0.3791738040000001</v>
+        <v>0.3728833674000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2346747756469792</v>
+        <v>0.2395177186122864</v>
       </c>
       <c r="T62">
-        <v>4.362004056512221</v>
+        <v>4.47385031437151</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.8134570500241587</v>
+        <v>-0.800121688548353</v>
       </c>
       <c r="W62">
-        <v>0.4276131723956966</v>
+        <v>0.4244686941597016</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6386,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-2.711523500080529</v>
+        <v>-2.667072295161176</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6394,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3523378136962097</v>
+        <v>0.3542378136962098</v>
       </c>
       <c r="C63">
-        <v>0.7151535563335796</v>
+        <v>0.673884835428836</v>
       </c>
       <c r="D63">
-        <v>0.9698635563335797</v>
+        <v>0.9667048354288362</v>
       </c>
       <c r="E63">
-        <v>1.99371</v>
+        <v>2.03182</v>
       </c>
       <c r="F63">
-        <v>2.32471</v>
+        <v>2.36282</v>
       </c>
       <c r="G63">
         <v>2.07</v>
@@ -6430,37 +6441,37 @@
         <v>-1.462</v>
       </c>
       <c r="M63">
-        <v>0.548166618</v>
+        <v>0.557152956</v>
       </c>
       <c r="N63">
-        <v>-2.010166618</v>
+        <v>-2.019152956</v>
       </c>
       <c r="O63">
-        <v>-0.6030499854</v>
+        <v>-0.6057458868</v>
       </c>
       <c r="P63">
-        <v>-1.4071166326</v>
+        <v>-1.4134070692</v>
       </c>
       <c r="Q63">
-        <v>0.3728833674000001</v>
+        <v>0.3665929307999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2395177186122864</v>
+        <v>0.2446155533126098</v>
       </c>
       <c r="T63">
-        <v>4.47385031437151</v>
+        <v>4.591583217381287</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.800121688548353</v>
+        <v>-0.7872165000233795</v>
       </c>
       <c r="W63">
-        <v>0.4244686941597016</v>
+        <v>0.4214256507055129</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6468,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-2.667072295161176</v>
+        <v>-2.624055000077932</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6476,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3542378136962098</v>
+        <v>0.3561378136962097</v>
       </c>
       <c r="C64">
-        <v>0.673884835428836</v>
+        <v>0.6326366228269085</v>
       </c>
       <c r="D64">
-        <v>0.9667048354288362</v>
+        <v>0.9635666228269085</v>
       </c>
       <c r="E64">
-        <v>2.03182</v>
+        <v>2.06993</v>
       </c>
       <c r="F64">
-        <v>2.36282</v>
+        <v>2.40093</v>
       </c>
       <c r="G64">
         <v>2.07</v>
@@ -6512,37 +6523,37 @@
         <v>-1.462</v>
       </c>
       <c r="M64">
-        <v>0.557152956</v>
+        <v>0.566139294</v>
       </c>
       <c r="N64">
-        <v>-2.019152956</v>
+        <v>-2.028139294</v>
       </c>
       <c r="O64">
-        <v>-0.6057458868</v>
+        <v>-0.6084417881999999</v>
       </c>
       <c r="P64">
-        <v>-1.4134070692</v>
+        <v>-1.4196975058</v>
       </c>
       <c r="Q64">
-        <v>0.3665929307999998</v>
+        <v>0.3603024942000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2446155533126098</v>
+        <v>0.249988946645383</v>
       </c>
       <c r="T64">
-        <v>4.591583217381287</v>
+        <v>4.715680061094295</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.7872165000233795</v>
+        <v>-0.7747210000230085</v>
       </c>
       <c r="W64">
-        <v>0.4214256507055129</v>
+        <v>0.4184792118054254</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6550,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-2.624055000077932</v>
+        <v>-2.582403333410028</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6558,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3561378136962097</v>
+        <v>0.3580378136962097</v>
       </c>
       <c r="C65">
-        <v>0.6326366228269085</v>
+        <v>0.5914087194458486</v>
       </c>
       <c r="D65">
-        <v>0.9635666228269085</v>
+        <v>0.9604487194458489</v>
       </c>
       <c r="E65">
-        <v>2.06993</v>
+        <v>2.10804</v>
       </c>
       <c r="F65">
-        <v>2.40093</v>
+        <v>2.43904</v>
       </c>
       <c r="G65">
         <v>2.07</v>
@@ -6594,37 +6605,37 @@
         <v>-1.462</v>
       </c>
       <c r="M65">
-        <v>0.566139294</v>
+        <v>0.575125632</v>
       </c>
       <c r="N65">
-        <v>-2.028139294</v>
+        <v>-2.037125632</v>
       </c>
       <c r="O65">
-        <v>-0.6084417881999999</v>
+        <v>-0.6111376895999999</v>
       </c>
       <c r="P65">
-        <v>-1.4196975058</v>
+        <v>-1.4259879424</v>
       </c>
       <c r="Q65">
-        <v>0.3603024942000002</v>
+        <v>0.3540120576000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.249988946645383</v>
+        <v>0.2556608618299769</v>
       </c>
       <c r="T65">
-        <v>4.715680061094295</v>
+        <v>4.846671173902469</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.7747210000230085</v>
+        <v>-0.7626159843976489</v>
       </c>
       <c r="W65">
-        <v>0.4184792118054254</v>
+        <v>0.4156248491209656</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6632,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-2.582403333410028</v>
+        <v>-2.542053281325496</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6640,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3580378136962097</v>
+        <v>0.3599378136962097</v>
       </c>
       <c r="C66">
-        <v>0.5914087194458486</v>
+        <v>0.5502009287721514</v>
       </c>
       <c r="D66">
-        <v>0.9604487194458489</v>
+        <v>0.9573509287721516</v>
       </c>
       <c r="E66">
-        <v>2.10804</v>
+        <v>2.14615</v>
       </c>
       <c r="F66">
-        <v>2.43904</v>
+        <v>2.47715</v>
       </c>
       <c r="G66">
         <v>2.07</v>
@@ -6676,37 +6687,37 @@
         <v>-1.462</v>
       </c>
       <c r="M66">
-        <v>0.575125632</v>
+        <v>0.58411197</v>
       </c>
       <c r="N66">
-        <v>-2.037125632</v>
+        <v>-2.04611197</v>
       </c>
       <c r="O66">
-        <v>-0.6111376895999999</v>
+        <v>-0.613833591</v>
       </c>
       <c r="P66">
-        <v>-1.4259879424</v>
+        <v>-1.432278379</v>
       </c>
       <c r="Q66">
-        <v>0.3540120576000001</v>
+        <v>0.347721621</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2556608618299769</v>
+        <v>0.2616568864536906</v>
       </c>
       <c r="T66">
-        <v>4.846671173902469</v>
+        <v>4.985147493156827</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.7626159843976489</v>
+        <v>-0.7508834307915312</v>
       </c>
       <c r="W66">
-        <v>0.4156248491209656</v>
+        <v>0.4128583129806431</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6714,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-2.542053281325496</v>
+        <v>-2.502944769305104</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6722,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3599378136962097</v>
+        <v>0.3618378136962097</v>
       </c>
       <c r="C67">
-        <v>0.5502009287721514</v>
+        <v>0.5090130568194651</v>
       </c>
       <c r="D67">
-        <v>0.9573509287721516</v>
+        <v>0.9542730568194653</v>
       </c>
       <c r="E67">
-        <v>2.14615</v>
+        <v>2.18426</v>
       </c>
       <c r="F67">
-        <v>2.47715</v>
+        <v>2.51526</v>
       </c>
       <c r="G67">
         <v>2.07</v>
@@ -6758,37 +6769,37 @@
         <v>-1.462</v>
       </c>
       <c r="M67">
-        <v>0.58411197</v>
+        <v>0.5930983080000001</v>
       </c>
       <c r="N67">
-        <v>-2.04611197</v>
+        <v>-2.055098308</v>
       </c>
       <c r="O67">
-        <v>-0.613833591</v>
+        <v>-0.6165294923999999</v>
       </c>
       <c r="P67">
-        <v>-1.432278379</v>
+        <v>-1.4385688156</v>
       </c>
       <c r="Q67">
-        <v>0.347721621</v>
+        <v>0.3414311844</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2616568864536906</v>
+        <v>0.2680056184082109</v>
       </c>
       <c r="T67">
-        <v>4.985147493156827</v>
+        <v>5.131769478249673</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.7508834307915312</v>
+        <v>-0.7395064091128716</v>
       </c>
       <c r="W67">
-        <v>0.4128583129806431</v>
+        <v>0.4101756112688151</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6796,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-2.502944769305104</v>
+        <v>-2.465021363709571</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6804,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3618378136962097</v>
+        <v>0.3637378136962097</v>
       </c>
       <c r="C68">
-        <v>0.5090130568194651</v>
+        <v>0.4678449120880988</v>
       </c>
       <c r="D68">
-        <v>0.9542730568194653</v>
+        <v>0.9512149120880991</v>
       </c>
       <c r="E68">
-        <v>2.18426</v>
+        <v>2.22237</v>
       </c>
       <c r="F68">
-        <v>2.51526</v>
+        <v>2.55337</v>
       </c>
       <c r="G68">
         <v>2.07</v>
@@ -6840,37 +6851,37 @@
         <v>-1.462</v>
       </c>
       <c r="M68">
-        <v>0.5930983080000001</v>
+        <v>0.6020846460000001</v>
       </c>
       <c r="N68">
-        <v>-2.055098308</v>
+        <v>-2.064084646</v>
       </c>
       <c r="O68">
-        <v>-0.6165294923999999</v>
+        <v>-0.6192253938</v>
       </c>
       <c r="P68">
-        <v>-1.4385688156</v>
+        <v>-1.4448592522</v>
       </c>
       <c r="Q68">
-        <v>0.3414311844</v>
+        <v>0.3351407477999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2680056184082109</v>
+        <v>0.2747391219963385</v>
       </c>
       <c r="T68">
-        <v>5.131769478249673</v>
+        <v>5.28727764425724</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.7395064091128716</v>
+        <v>-0.7284690000216347</v>
       </c>
       <c r="W68">
-        <v>0.4101756112688151</v>
+        <v>0.4075729902051015</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6878,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-2.465021363709571</v>
+        <v>-2.428230000072115</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6886,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3637378136962097</v>
+        <v>0.3656378136962097</v>
       </c>
       <c r="C69">
-        <v>0.4678449120880988</v>
+        <v>0.4266963055253052</v>
       </c>
       <c r="D69">
-        <v>0.9512149120880991</v>
+        <v>0.9481763055253056</v>
       </c>
       <c r="E69">
-        <v>2.22237</v>
+        <v>2.26048</v>
       </c>
       <c r="F69">
-        <v>2.55337</v>
+        <v>2.59148</v>
       </c>
       <c r="G69">
         <v>2.07</v>
@@ -6922,37 +6933,37 @@
         <v>-1.462</v>
       </c>
       <c r="M69">
-        <v>0.6020846460000001</v>
+        <v>0.611070984</v>
       </c>
       <c r="N69">
-        <v>-2.064084646</v>
+        <v>-2.073070984</v>
       </c>
       <c r="O69">
-        <v>-0.6192253938</v>
+        <v>-0.6219212952000001</v>
       </c>
       <c r="P69">
-        <v>-1.4448592522</v>
+        <v>-1.4511496888</v>
       </c>
       <c r="Q69">
-        <v>0.3351407477999999</v>
+        <v>0.3288503111999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2747391219963385</v>
+        <v>0.2818934695587241</v>
       </c>
       <c r="T69">
-        <v>5.28727764425724</v>
+        <v>5.45250507064028</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.7284690000216347</v>
+        <v>-0.7177562206095519</v>
       </c>
       <c r="W69">
-        <v>0.4075729902051015</v>
+        <v>0.4050469168197324</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6960,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-2.428230000072115</v>
+        <v>-2.392520735365173</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6968,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3656378136962097</v>
+        <v>0.3675378136962097</v>
       </c>
       <c r="C70">
-        <v>0.4266963055253052</v>
+        <v>0.3855670504863218</v>
       </c>
       <c r="D70">
-        <v>0.9481763055253056</v>
+        <v>0.9451570504863223</v>
       </c>
       <c r="E70">
-        <v>2.26048</v>
+        <v>2.29859</v>
       </c>
       <c r="F70">
-        <v>2.59148</v>
+        <v>2.62959</v>
       </c>
       <c r="G70">
         <v>2.07</v>
@@ -7004,37 +7015,37 @@
         <v>-1.462</v>
       </c>
       <c r="M70">
-        <v>0.611070984</v>
+        <v>0.6200573220000001</v>
       </c>
       <c r="N70">
-        <v>-2.073070984</v>
+        <v>-2.082057322</v>
       </c>
       <c r="O70">
-        <v>-0.6219212952000001</v>
+        <v>-0.6246171965999999</v>
       </c>
       <c r="P70">
-        <v>-1.4511496888</v>
+        <v>-1.4574401254</v>
       </c>
       <c r="Q70">
-        <v>0.3288503111999999</v>
+        <v>0.3225598746000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2818934695587241</v>
+        <v>0.2895093879315862</v>
       </c>
       <c r="T70">
-        <v>5.45250507064028</v>
+        <v>5.628392330983515</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.7177562206095519</v>
+        <v>-0.7073539565427467</v>
       </c>
       <c r="W70">
-        <v>0.4050469168197324</v>
+        <v>0.4025940629527797</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7042,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-2.392520735365173</v>
+        <v>-2.357846521809155</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7050,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3675378136962097</v>
+        <v>0.3694378136962096</v>
       </c>
       <c r="C71">
-        <v>0.3855670504863218</v>
+        <v>0.3444569626961536</v>
       </c>
       <c r="D71">
-        <v>0.9451570504863223</v>
+        <v>0.9421569626961539</v>
       </c>
       <c r="E71">
-        <v>2.29859</v>
+        <v>2.3367</v>
       </c>
       <c r="F71">
-        <v>2.62959</v>
+        <v>2.6677</v>
       </c>
       <c r="G71">
         <v>2.07</v>
@@ -7086,37 +7097,37 @@
         <v>-1.462</v>
       </c>
       <c r="M71">
-        <v>0.6200573220000001</v>
+        <v>0.6290436600000001</v>
       </c>
       <c r="N71">
-        <v>-2.082057322</v>
+        <v>-2.09104366</v>
       </c>
       <c r="O71">
-        <v>-0.6246171965999999</v>
+        <v>-0.627313098</v>
       </c>
       <c r="P71">
-        <v>-1.4574401254</v>
+        <v>-1.463730562</v>
       </c>
       <c r="Q71">
-        <v>0.3225598746000002</v>
+        <v>0.3162694380000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2895093879315862</v>
+        <v>0.2976330341959724</v>
       </c>
       <c r="T71">
-        <v>5.628392330983515</v>
+        <v>5.816005408682964</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.7073539565427467</v>
+        <v>-0.6972489000207074</v>
       </c>
       <c r="W71">
-        <v>0.4025940629527797</v>
+        <v>0.4002112906248828</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7124,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-2.357846521809155</v>
+        <v>-2.324163000069025</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7132,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3694378136962096</v>
+        <v>0.3713378136962098</v>
       </c>
       <c r="C72">
-        <v>0.3444569626961536</v>
+        <v>0.303365860212081</v>
       </c>
       <c r="D72">
-        <v>0.9421569626961539</v>
+        <v>0.9391758602120811</v>
       </c>
       <c r="E72">
-        <v>2.3367</v>
+        <v>2.37481</v>
       </c>
       <c r="F72">
-        <v>2.6677</v>
+        <v>2.70581</v>
       </c>
       <c r="G72">
         <v>2.07</v>
@@ -7168,37 +7179,37 @@
         <v>-1.462</v>
       </c>
       <c r="M72">
-        <v>0.6290436600000001</v>
+        <v>0.638029998</v>
       </c>
       <c r="N72">
-        <v>-2.09104366</v>
+        <v>-2.100029998</v>
       </c>
       <c r="O72">
-        <v>-0.627313098</v>
+        <v>-0.6300089994</v>
       </c>
       <c r="P72">
-        <v>-1.463730562</v>
+        <v>-1.4700209986</v>
       </c>
       <c r="Q72">
-        <v>0.3162694380000002</v>
+        <v>0.3099790013999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2976330341959724</v>
+        <v>0.306316931926868</v>
       </c>
       <c r="T72">
-        <v>5.816005408682964</v>
+        <v>6.016557319327205</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.6972489000207074</v>
+        <v>-0.6874284929781624</v>
       </c>
       <c r="W72">
-        <v>0.4002112906248828</v>
+        <v>0.3978956386442507</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7206,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-2.324163000069025</v>
+        <v>-2.291428309927208</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7214,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3713378136962097</v>
+        <v>0.3732378136962097</v>
       </c>
       <c r="C73">
-        <v>0.3033658602120815</v>
+        <v>0.2622935633868813</v>
       </c>
       <c r="D73">
-        <v>0.9391758602120811</v>
+        <v>0.9362135633868811</v>
       </c>
       <c r="E73">
-        <v>2.37481</v>
+        <v>2.41292</v>
       </c>
       <c r="F73">
-        <v>2.70581</v>
+        <v>2.74392</v>
       </c>
       <c r="G73">
         <v>2.07</v>
@@ -7250,37 +7261,37 @@
         <v>-1.462</v>
       </c>
       <c r="M73">
-        <v>0.6380299979999999</v>
+        <v>0.647016336</v>
       </c>
       <c r="N73">
-        <v>-2.100029998</v>
+        <v>-2.109016336</v>
       </c>
       <c r="O73">
-        <v>-0.6300089994</v>
+        <v>-0.6327049008</v>
       </c>
       <c r="P73">
-        <v>-1.4700209986</v>
+        <v>-1.4763114352</v>
       </c>
       <c r="Q73">
-        <v>0.3099790013999999</v>
+        <v>0.3036885648000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3063169319268679</v>
+        <v>0.3156211080671132</v>
       </c>
       <c r="T73">
-        <v>6.016557319327204</v>
+        <v>6.231434366446032</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.6874284929781624</v>
+        <v>-0.6778808750201324</v>
       </c>
       <c r="W73">
-        <v>0.3978956386442507</v>
+        <v>0.3956443103297472</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7288,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-2.291428309927209</v>
+        <v>-2.259602916733775</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7296,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3732378136962097</v>
+        <v>0.3751378136962097</v>
       </c>
       <c r="C74">
-        <v>0.2622935633868813</v>
+        <v>0.221239894832737</v>
       </c>
       <c r="D74">
-        <v>0.9362135633868811</v>
+        <v>0.9332698948327369</v>
       </c>
       <c r="E74">
-        <v>2.41292</v>
+        <v>2.45103</v>
       </c>
       <c r="F74">
-        <v>2.74392</v>
+        <v>2.78203</v>
       </c>
       <c r="G74">
         <v>2.07</v>
@@ -7332,37 +7343,37 @@
         <v>-1.462</v>
       </c>
       <c r="M74">
-        <v>0.647016336</v>
+        <v>0.656002674</v>
       </c>
       <c r="N74">
-        <v>-2.109016336</v>
+        <v>-2.118002674</v>
       </c>
       <c r="O74">
-        <v>-0.6327049008</v>
+        <v>-0.6354008021999999</v>
       </c>
       <c r="P74">
-        <v>-1.4763114352</v>
+        <v>-1.4826018718</v>
       </c>
       <c r="Q74">
-        <v>0.3036885648000001</v>
+        <v>0.2973981282</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3156211080671132</v>
+        <v>0.3256144824399693</v>
       </c>
       <c r="T74">
-        <v>6.231434366446032</v>
+        <v>6.462228231869958</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.6778808750201324</v>
+        <v>-0.668594835636295</v>
       </c>
       <c r="W74">
-        <v>0.3956443103297472</v>
+        <v>0.3934546622430384</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7370,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-2.259602916733775</v>
+        <v>-2.228649452120983</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7378,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3751378136962097</v>
+        <v>0.3770378136962096</v>
       </c>
       <c r="C75">
-        <v>0.221239894832737</v>
+        <v>0.1802046793858292</v>
       </c>
       <c r="D75">
-        <v>0.9332698948327369</v>
+        <v>0.9303446793858293</v>
       </c>
       <c r="E75">
-        <v>2.45103</v>
+        <v>2.48914</v>
       </c>
       <c r="F75">
-        <v>2.78203</v>
+        <v>2.82014</v>
       </c>
       <c r="G75">
         <v>2.07</v>
@@ -7414,37 +7425,37 @@
         <v>-1.462</v>
       </c>
       <c r="M75">
-        <v>0.656002674</v>
+        <v>0.664989012</v>
       </c>
       <c r="N75">
-        <v>-2.118002674</v>
+        <v>-2.126989012</v>
       </c>
       <c r="O75">
-        <v>-0.6354008021999999</v>
+        <v>-0.6380967036</v>
       </c>
       <c r="P75">
-        <v>-1.4826018718</v>
+        <v>-1.4888923084</v>
       </c>
       <c r="Q75">
-        <v>0.2973981282</v>
+        <v>0.2911076915999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3256144824399693</v>
+        <v>0.3363765779184296</v>
       </c>
       <c r="T75">
-        <v>6.462228231869958</v>
+        <v>6.710775471557264</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.668594835636295</v>
+        <v>-0.6595597702898585</v>
       </c>
       <c r="W75">
-        <v>0.3934546622430384</v>
+        <v>0.3913241938343486</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7452,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-2.228649452120983</v>
+        <v>-2.198532567632862</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7460,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3770378136962096</v>
+        <v>0.3789378136962097</v>
       </c>
       <c r="C76">
-        <v>0.1802046793858292</v>
+        <v>0.1391877440715925</v>
       </c>
       <c r="D76">
-        <v>0.9303446793858293</v>
+        <v>0.9274377440715927</v>
       </c>
       <c r="E76">
-        <v>2.48914</v>
+        <v>2.52725</v>
       </c>
       <c r="F76">
-        <v>2.82014</v>
+        <v>2.85825</v>
       </c>
       <c r="G76">
         <v>2.07</v>
@@ -7496,37 +7507,37 @@
         <v>-1.462</v>
       </c>
       <c r="M76">
-        <v>0.664989012</v>
+        <v>0.67397535</v>
       </c>
       <c r="N76">
-        <v>-2.126989012</v>
+        <v>-2.13597535</v>
       </c>
       <c r="O76">
-        <v>-0.6380967036</v>
+        <v>-0.6407926049999999</v>
       </c>
       <c r="P76">
-        <v>-1.4888923084</v>
+        <v>-1.495182745</v>
       </c>
       <c r="Q76">
-        <v>0.2911076915999999</v>
+        <v>0.2848172550000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3363765779184296</v>
+        <v>0.3479996410351668</v>
       </c>
       <c r="T76">
-        <v>6.710775471557264</v>
+        <v>6.979206490419556</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.6595597702898585</v>
+        <v>-0.6507656400193271</v>
       </c>
       <c r="W76">
-        <v>0.3913241938343486</v>
+        <v>0.3892505379165573</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7534,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-2.198532567632862</v>
+        <v>-2.169218800064423</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7542,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3789378136962097</v>
+        <v>0.3808378136962097</v>
       </c>
       <c r="C77">
-        <v>0.1391877440715925</v>
+        <v>0.09818891807061725</v>
       </c>
       <c r="D77">
-        <v>0.9274377440715927</v>
+        <v>0.9245489180706173</v>
       </c>
       <c r="E77">
-        <v>2.52725</v>
+        <v>2.56536</v>
       </c>
       <c r="F77">
-        <v>2.85825</v>
+        <v>2.89636</v>
       </c>
       <c r="G77">
         <v>2.07</v>
@@ -7578,37 +7589,37 @@
         <v>-1.462</v>
       </c>
       <c r="M77">
-        <v>0.67397535</v>
+        <v>0.682961688</v>
       </c>
       <c r="N77">
-        <v>-2.13597535</v>
+        <v>-2.144961688</v>
       </c>
       <c r="O77">
-        <v>-0.6407926049999999</v>
+        <v>-0.6434885064</v>
       </c>
       <c r="P77">
-        <v>-1.495182745</v>
+        <v>-1.5014731816</v>
       </c>
       <c r="Q77">
-        <v>0.2848172550000001</v>
+        <v>0.2785268184</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3479996410351668</v>
+        <v>0.3605912927449655</v>
       </c>
       <c r="T77">
-        <v>6.979206490419556</v>
+        <v>7.270006760853705</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.6507656400193271</v>
+        <v>-0.6422029342295991</v>
       </c>
       <c r="W77">
-        <v>0.3892505379165573</v>
+        <v>0.3872314518913395</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7616,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-2.169218800064423</v>
+        <v>-2.140676447431997</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7624,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3808378136962097</v>
+        <v>0.3827378136962097</v>
       </c>
       <c r="C78">
-        <v>0.09818891807061725</v>
+        <v>0.05720803268518981</v>
       </c>
       <c r="D78">
-        <v>0.9245489180706173</v>
+        <v>0.92167803268519</v>
       </c>
       <c r="E78">
-        <v>2.56536</v>
+        <v>2.60347</v>
       </c>
       <c r="F78">
-        <v>2.89636</v>
+        <v>2.93447</v>
       </c>
       <c r="G78">
         <v>2.07</v>
@@ -7660,37 +7671,37 @@
         <v>-1.462</v>
       </c>
       <c r="M78">
-        <v>0.682961688</v>
+        <v>0.691948026</v>
       </c>
       <c r="N78">
-        <v>-2.144961688</v>
+        <v>-2.153948026</v>
       </c>
       <c r="O78">
-        <v>-0.6434885064</v>
+        <v>-0.6461844078</v>
       </c>
       <c r="P78">
-        <v>-1.5014731816</v>
+        <v>-1.5077636182</v>
       </c>
       <c r="Q78">
-        <v>0.2785268184</v>
+        <v>0.2722363817999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3605912927449655</v>
+        <v>0.3742778706903988</v>
       </c>
       <c r="T78">
-        <v>7.270006760853705</v>
+        <v>7.586094011325605</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.6422029342295991</v>
+        <v>-0.6338626363824614</v>
       </c>
       <c r="W78">
-        <v>0.3872314518913395</v>
+        <v>0.3852648096589845</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7698,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-2.140676447431997</v>
+        <v>-2.112875454608205</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7706,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3827378136962097</v>
+        <v>0.3846378136962097</v>
       </c>
       <c r="C79">
-        <v>0.05720803268518981</v>
+        <v>0.01624492130645416</v>
       </c>
       <c r="D79">
-        <v>0.92167803268519</v>
+        <v>0.9188249213064544</v>
       </c>
       <c r="E79">
-        <v>2.60347</v>
+        <v>2.64158</v>
       </c>
       <c r="F79">
-        <v>2.93447</v>
+        <v>2.97258</v>
       </c>
       <c r="G79">
         <v>2.07</v>
@@ -7742,37 +7753,37 @@
         <v>-1.462</v>
       </c>
       <c r="M79">
-        <v>0.691948026</v>
+        <v>0.7009343640000001</v>
       </c>
       <c r="N79">
-        <v>-2.153948026</v>
+        <v>-2.162934364</v>
       </c>
       <c r="O79">
-        <v>-0.6461844078</v>
+        <v>-0.6488803091999999</v>
       </c>
       <c r="P79">
-        <v>-1.5077636182</v>
+        <v>-1.5140540548</v>
       </c>
       <c r="Q79">
-        <v>0.2722363817999998</v>
+        <v>0.2659459452000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3742778706903988</v>
+        <v>0.3892086829945078</v>
       </c>
       <c r="T79">
-        <v>7.586094011325605</v>
+        <v>7.93091646638586</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.6338626363824614</v>
+        <v>-0.625736192326276</v>
       </c>
       <c r="W79">
-        <v>0.3852648096589845</v>
+        <v>0.3833485941505359</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7780,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-2.112875454608205</v>
+        <v>-2.085787307754253</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7788,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3846378136962097</v>
+        <v>0.3865378136962097</v>
       </c>
       <c r="C80">
-        <v>0.01624492130645416</v>
+        <v>-0.02470058061782066</v>
       </c>
       <c r="D80">
-        <v>0.9188249213064544</v>
+        <v>0.9159894193821796</v>
       </c>
       <c r="E80">
-        <v>2.64158</v>
+        <v>2.67969</v>
       </c>
       <c r="F80">
-        <v>2.97258</v>
+        <v>3.01069</v>
       </c>
       <c r="G80">
         <v>2.07</v>
@@ -7824,37 +7835,37 @@
         <v>-1.462</v>
       </c>
       <c r="M80">
-        <v>0.7009343640000001</v>
+        <v>0.7099207020000001</v>
       </c>
       <c r="N80">
-        <v>-2.162934364</v>
+        <v>-2.171920702</v>
       </c>
       <c r="O80">
-        <v>-0.6488803091999999</v>
+        <v>-0.6515762105999999</v>
       </c>
       <c r="P80">
-        <v>-1.5140540548</v>
+        <v>-1.5203444914</v>
       </c>
       <c r="Q80">
-        <v>0.2659459452000001</v>
+        <v>0.2596555086000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3892086829945078</v>
+        <v>0.4055614774228177</v>
       </c>
       <c r="T80">
-        <v>7.93091646638586</v>
+        <v>8.308579155261377</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.625736192326276</v>
+        <v>-0.6178154810310066</v>
       </c>
       <c r="W80">
-        <v>0.3833485941505359</v>
+        <v>0.3814808904271114</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7862,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-2.085787307754253</v>
+        <v>-2.059384936770022</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7870,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3865378136962097</v>
+        <v>0.3884378136962097</v>
       </c>
       <c r="C81">
-        <v>-0.02470058061782066</v>
+        <v>-0.06562863561487609</v>
       </c>
       <c r="D81">
-        <v>0.9159894193821796</v>
+        <v>0.913171364385124</v>
       </c>
       <c r="E81">
-        <v>2.67969</v>
+        <v>2.7178</v>
       </c>
       <c r="F81">
-        <v>3.01069</v>
+        <v>3.0488</v>
       </c>
       <c r="G81">
         <v>2.07</v>
@@ -7906,37 +7917,37 @@
         <v>-1.462</v>
       </c>
       <c r="M81">
-        <v>0.7099207020000001</v>
+        <v>0.7189070400000001</v>
       </c>
       <c r="N81">
-        <v>-2.171920702</v>
+        <v>-2.18090704</v>
       </c>
       <c r="O81">
-        <v>-0.6515762105999999</v>
+        <v>-0.654272112</v>
       </c>
       <c r="P81">
-        <v>-1.5203444914</v>
+        <v>-1.526634928</v>
       </c>
       <c r="Q81">
-        <v>0.2596555086000001</v>
+        <v>0.253365072</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4055614774228177</v>
+        <v>0.4235495512939585</v>
       </c>
       <c r="T81">
-        <v>8.308579155261377</v>
+        <v>8.724008113024446</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.6178154810310066</v>
+        <v>-0.6100927875181191</v>
       </c>
       <c r="W81">
-        <v>0.3814808904271114</v>
+        <v>0.3796598792967725</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7944,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-2.059384936770022</v>
+        <v>-2.033642625060397</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7952,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3884378136962097</v>
+        <v>0.3903378136962097</v>
       </c>
       <c r="C82">
-        <v>-0.06562863561487609</v>
+        <v>-0.1065394042180179</v>
       </c>
       <c r="D82">
-        <v>0.913171364385124</v>
+        <v>0.9103705957819822</v>
       </c>
       <c r="E82">
-        <v>2.7178</v>
+        <v>2.75591</v>
       </c>
       <c r="F82">
-        <v>3.0488</v>
+        <v>3.08691</v>
       </c>
       <c r="G82">
         <v>2.07</v>
@@ -7988,37 +7999,37 @@
         <v>-1.462</v>
       </c>
       <c r="M82">
-        <v>0.7189070400000001</v>
+        <v>0.7278933780000001</v>
       </c>
       <c r="N82">
-        <v>-2.18090704</v>
+        <v>-2.189893378</v>
       </c>
       <c r="O82">
-        <v>-0.654272112</v>
+        <v>-0.6569680133999999</v>
       </c>
       <c r="P82">
-        <v>-1.526634928</v>
+        <v>-1.5329253646</v>
       </c>
       <c r="Q82">
-        <v>0.253365072</v>
+        <v>0.2470746354</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4235495512939585</v>
+        <v>0.4434311066252196</v>
       </c>
       <c r="T82">
-        <v>8.724008113024446</v>
+        <v>9.183166434762576</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.6100927875181191</v>
+        <v>-0.6025607777956732</v>
       </c>
       <c r="W82">
-        <v>0.3796598792967725</v>
+        <v>0.3778838314042198</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8026,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-2.033642625060397</v>
+        <v>-2.008535925985577</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8034,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3903378136962097</v>
+        <v>0.3922378136962098</v>
       </c>
       <c r="C83">
-        <v>-0.1065394042180179</v>
+        <v>-0.1474330449971015</v>
       </c>
       <c r="D83">
-        <v>0.9103705957819822</v>
+        <v>0.907586955002899</v>
       </c>
       <c r="E83">
-        <v>2.75591</v>
+        <v>2.79402</v>
       </c>
       <c r="F83">
-        <v>3.08691</v>
+        <v>3.12502</v>
       </c>
       <c r="G83">
         <v>2.07</v>
@@ -8070,37 +8081,37 @@
         <v>-1.462</v>
       </c>
       <c r="M83">
-        <v>0.7278933780000001</v>
+        <v>0.736879716</v>
       </c>
       <c r="N83">
-        <v>-2.189893378</v>
+        <v>-2.198879716</v>
       </c>
       <c r="O83">
-        <v>-0.6569680133999999</v>
+        <v>-0.6596639148</v>
       </c>
       <c r="P83">
-        <v>-1.5329253646</v>
+        <v>-1.5392158012</v>
       </c>
       <c r="Q83">
-        <v>0.2470746354</v>
+        <v>0.2407841987999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4434311066252196</v>
+        <v>0.4655217236599541</v>
       </c>
       <c r="T83">
-        <v>9.183166434762576</v>
+        <v>9.693342347804943</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.6025607777956732</v>
+        <v>-0.5952124756274333</v>
       </c>
       <c r="W83">
-        <v>0.3778838314042198</v>
+        <v>0.3761511017529488</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8108,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-2.008535925985577</v>
+        <v>-1.984041585424777</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8116,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3922378136962098</v>
+        <v>0.3941378136962097</v>
       </c>
       <c r="C84">
-        <v>-0.1474330449971015</v>
+        <v>-0.1883097145884554</v>
       </c>
       <c r="D84">
-        <v>0.907586955002899</v>
+        <v>0.9048202854115449</v>
       </c>
       <c r="E84">
-        <v>2.79402</v>
+        <v>2.83213</v>
       </c>
       <c r="F84">
-        <v>3.12502</v>
+        <v>3.16313</v>
       </c>
       <c r="G84">
         <v>2.07</v>
@@ -8152,37 +8163,37 @@
         <v>-1.462</v>
       </c>
       <c r="M84">
-        <v>0.736879716</v>
+        <v>0.7458660540000001</v>
       </c>
       <c r="N84">
-        <v>-2.198879716</v>
+        <v>-2.207866054</v>
       </c>
       <c r="O84">
-        <v>-0.6596639148</v>
+        <v>-0.6623598162000001</v>
       </c>
       <c r="P84">
-        <v>-1.5392158012</v>
+        <v>-1.5455062378</v>
       </c>
       <c r="Q84">
-        <v>0.2407841987999999</v>
+        <v>0.2344937621999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4655217236599541</v>
+        <v>0.4902112368164219</v>
       </c>
       <c r="T84">
-        <v>9.693342347804943</v>
+        <v>10.26353895649935</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.5952124756274333</v>
+        <v>-0.5880412409813196</v>
       </c>
       <c r="W84">
-        <v>0.3761511017529488</v>
+        <v>0.3744601246233952</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8190,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-1.984041585424777</v>
+        <v>-1.960137469937732</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8198,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3941378136962097</v>
+        <v>0.3960378136962097</v>
       </c>
       <c r="C85">
-        <v>-0.1883097145884554</v>
+        <v>-0.2291695677242682</v>
       </c>
       <c r="D85">
-        <v>0.9048202854115449</v>
+        <v>0.9020704322757325</v>
       </c>
       <c r="E85">
-        <v>2.83213</v>
+        <v>2.87024</v>
       </c>
       <c r="F85">
-        <v>3.16313</v>
+        <v>3.20124</v>
       </c>
       <c r="G85">
         <v>2.07</v>
@@ -8234,37 +8245,37 @@
         <v>-1.462</v>
       </c>
       <c r="M85">
-        <v>0.7458660540000001</v>
+        <v>0.7548523920000001</v>
       </c>
       <c r="N85">
-        <v>-2.207866054</v>
+        <v>-2.216852392</v>
       </c>
       <c r="O85">
-        <v>-0.6623598162000001</v>
+        <v>-0.6650557175999999</v>
       </c>
       <c r="P85">
-        <v>-1.5455062378</v>
+        <v>-1.5517966744</v>
       </c>
       <c r="Q85">
-        <v>0.2344937621999998</v>
+        <v>0.2282033256000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4902112368164219</v>
+        <v>0.5179869391174483</v>
       </c>
       <c r="T85">
-        <v>10.26353895649935</v>
+        <v>10.90501014128056</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.5880412409813196</v>
+        <v>-0.5810407500172562</v>
       </c>
       <c r="W85">
-        <v>0.3744601246233952</v>
+        <v>0.372809408854069</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8272,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-1.960137469937732</v>
+        <v>-1.93680250005752</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8280,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3960378136962097</v>
+        <v>0.3979378136962097</v>
       </c>
       <c r="C86">
-        <v>-0.2291695677242678</v>
+        <v>-0.2700127572614281</v>
       </c>
       <c r="D86">
-        <v>0.9020704322757325</v>
+        <v>0.899337242738572</v>
       </c>
       <c r="E86">
-        <v>2.87024</v>
+        <v>2.90835</v>
       </c>
       <c r="F86">
-        <v>3.20124</v>
+        <v>3.23935</v>
       </c>
       <c r="G86">
         <v>2.07</v>
@@ -8316,37 +8327,37 @@
         <v>-1.462</v>
       </c>
       <c r="M86">
-        <v>0.754852392</v>
+        <v>0.76383873</v>
       </c>
       <c r="N86">
-        <v>-2.216852392</v>
+        <v>-2.22583873</v>
       </c>
       <c r="O86">
-        <v>-0.6650557175999999</v>
+        <v>-0.667751619</v>
       </c>
       <c r="P86">
-        <v>-1.5517966744</v>
+        <v>-1.558087111</v>
       </c>
       <c r="Q86">
-        <v>0.2282033256000002</v>
+        <v>0.2219128890000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5179869391174481</v>
+        <v>0.5494660683919446</v>
       </c>
       <c r="T86">
-        <v>10.90501014128055</v>
+        <v>11.63201081736593</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.5810407500172563</v>
+        <v>-0.5742049764876416</v>
       </c>
       <c r="W86">
-        <v>0.372809408854069</v>
+        <v>0.3711975334557859</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8354,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-1.936802500057521</v>
+        <v>-1.914016588292138</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8362,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3979378136962097</v>
+        <v>0.3998378136962097</v>
       </c>
       <c r="C87">
-        <v>-0.2700127572614281</v>
+        <v>-0.3108394342098548</v>
       </c>
       <c r="D87">
-        <v>0.899337242738572</v>
+        <v>0.8966205657901456</v>
       </c>
       <c r="E87">
-        <v>2.90835</v>
+        <v>2.94646</v>
       </c>
       <c r="F87">
-        <v>3.23935</v>
+        <v>3.27746</v>
       </c>
       <c r="G87">
         <v>2.07</v>
@@ -8398,37 +8409,37 @@
         <v>-1.462</v>
       </c>
       <c r="M87">
-        <v>0.76383873</v>
+        <v>0.7728250680000001</v>
       </c>
       <c r="N87">
-        <v>-2.22583873</v>
+        <v>-2.234825068</v>
       </c>
       <c r="O87">
-        <v>-0.667751619</v>
+        <v>-0.6704475204</v>
       </c>
       <c r="P87">
-        <v>-1.558087111</v>
+        <v>-1.5643775476</v>
       </c>
       <c r="Q87">
-        <v>0.2219128890000002</v>
+        <v>0.2156224523999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5494660683919446</v>
+        <v>0.5854422161342264</v>
       </c>
       <c r="T87">
-        <v>11.63201081736593</v>
+        <v>12.46286873289206</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.5742049764876416</v>
+        <v>-0.5675281744354597</v>
       </c>
       <c r="W87">
-        <v>0.3711975334557859</v>
+        <v>0.3696231435318814</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8436,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-1.914016588292138</v>
+        <v>-1.891760581451532</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8444,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3998378136962097</v>
+        <v>0.4017378136962096</v>
       </c>
       <c r="C88">
-        <v>-0.3108394342098548</v>
+        <v>-0.3516497477603044</v>
       </c>
       <c r="D88">
-        <v>0.8966205657901456</v>
+        <v>0.8939202522396957</v>
       </c>
       <c r="E88">
-        <v>2.94646</v>
+        <v>2.98457</v>
       </c>
       <c r="F88">
-        <v>3.27746</v>
+        <v>3.31557</v>
       </c>
       <c r="G88">
         <v>2.07</v>
@@ -8480,37 +8491,37 @@
         <v>-1.462</v>
       </c>
       <c r="M88">
-        <v>0.7728250680000001</v>
+        <v>0.7818114060000001</v>
       </c>
       <c r="N88">
-        <v>-2.234825068</v>
+        <v>-2.243811406</v>
       </c>
       <c r="O88">
-        <v>-0.6704475204</v>
+        <v>-0.6731434218</v>
       </c>
       <c r="P88">
-        <v>-1.5643775476</v>
+        <v>-1.5706679842</v>
       </c>
       <c r="Q88">
-        <v>0.2156224523999999</v>
+        <v>0.2093320158</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5854422161342264</v>
+        <v>0.6269531558368591</v>
       </c>
       <c r="T88">
-        <v>12.46286873289206</v>
+        <v>13.42155094311453</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.5675281744354597</v>
+        <v>-0.5610048620856267</v>
       </c>
       <c r="W88">
-        <v>0.3696231435318814</v>
+        <v>0.3680849464797908</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8518,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-1.891760581451532</v>
+        <v>-1.870016206952089</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8526,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.4017378136962096</v>
+        <v>0.4036378136962097</v>
       </c>
       <c r="C89">
-        <v>-0.3516497477603044</v>
+        <v>-0.3924438453116856</v>
       </c>
       <c r="D89">
-        <v>0.8939202522396957</v>
+        <v>0.8912361546883144</v>
       </c>
       <c r="E89">
-        <v>2.98457</v>
+        <v>3.02268</v>
       </c>
       <c r="F89">
-        <v>3.31557</v>
+        <v>3.35368</v>
       </c>
       <c r="G89">
         <v>2.07</v>
@@ -8562,37 +8573,37 @@
         <v>-1.462</v>
       </c>
       <c r="M89">
-        <v>0.7818114060000001</v>
+        <v>0.790797744</v>
       </c>
       <c r="N89">
-        <v>-2.243811406</v>
+        <v>-2.252797744</v>
       </c>
       <c r="O89">
-        <v>-0.6731434218</v>
+        <v>-0.6758393232</v>
       </c>
       <c r="P89">
-        <v>-1.5706679842</v>
+        <v>-1.5769584208</v>
       </c>
       <c r="Q89">
-        <v>0.2093320158</v>
+        <v>0.2030415792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6269531558368591</v>
+        <v>0.6753825854899308</v>
       </c>
       <c r="T89">
-        <v>13.42155094311453</v>
+        <v>14.54001352170741</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.5610048620856267</v>
+        <v>-0.5546298068346537</v>
       </c>
       <c r="W89">
-        <v>0.3680849464797908</v>
+        <v>0.3665817084516113</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8600,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-1.870016206952089</v>
+        <v>-1.848766022782179</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8608,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.4036378136962097</v>
+        <v>0.4055378136962097</v>
       </c>
       <c r="C90">
-        <v>-0.3924438453116856</v>
+        <v>-0.4332218724978794</v>
       </c>
       <c r="D90">
-        <v>0.8912361546883144</v>
+        <v>0.8885681275021208</v>
       </c>
       <c r="E90">
-        <v>3.02268</v>
+        <v>3.06079</v>
       </c>
       <c r="F90">
-        <v>3.35368</v>
+        <v>3.39179</v>
       </c>
       <c r="G90">
         <v>2.07</v>
@@ -8644,37 +8655,37 @@
         <v>-1.462</v>
       </c>
       <c r="M90">
-        <v>0.790797744</v>
+        <v>0.799784082</v>
       </c>
       <c r="N90">
-        <v>-2.252797744</v>
+        <v>-2.261784082</v>
       </c>
       <c r="O90">
-        <v>-0.6758393232</v>
+        <v>-0.6785352246</v>
       </c>
       <c r="P90">
-        <v>-1.5769584208</v>
+        <v>-1.5832488574</v>
       </c>
       <c r="Q90">
-        <v>0.2030415792</v>
+        <v>0.1967511425999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6753825854899308</v>
+        <v>0.7326173659890155</v>
       </c>
       <c r="T90">
-        <v>14.54001352170741</v>
+        <v>15.86183293277172</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.5546298068346537</v>
+        <v>-0.548398011252242</v>
       </c>
       <c r="W90">
-        <v>0.3665817084516113</v>
+        <v>0.3651122510532787</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8682,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-1.848766022782179</v>
+        <v>-1.827993370840807</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8690,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.4055378136962097</v>
+        <v>0.4074378136962097</v>
       </c>
       <c r="C91">
-        <v>-0.4332218724978794</v>
+        <v>-0.4739839732140756</v>
       </c>
       <c r="D91">
-        <v>0.8885681275021208</v>
+        <v>0.8859160267859245</v>
       </c>
       <c r="E91">
-        <v>3.06079</v>
+        <v>3.0989</v>
       </c>
       <c r="F91">
-        <v>3.39179</v>
+        <v>3.4299</v>
       </c>
       <c r="G91">
         <v>2.07</v>
@@ -8726,37 +8737,37 @@
         <v>-1.462</v>
       </c>
       <c r="M91">
-        <v>0.799784082</v>
+        <v>0.80877042</v>
       </c>
       <c r="N91">
-        <v>-2.261784082</v>
+        <v>-2.27077042</v>
       </c>
       <c r="O91">
-        <v>-0.6785352246</v>
+        <v>-0.6812311259999999</v>
       </c>
       <c r="P91">
-        <v>-1.5832488574</v>
+        <v>-1.589539294</v>
       </c>
       <c r="Q91">
-        <v>0.1967511425999999</v>
+        <v>0.1904607060000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7326173659890155</v>
+        <v>0.801299102587917</v>
       </c>
       <c r="T91">
-        <v>15.86183293277172</v>
+        <v>17.44801622604889</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.548398011252242</v>
+        <v>-0.5423047000161059</v>
       </c>
       <c r="W91">
-        <v>0.3651122510532787</v>
+        <v>0.3636754482637978</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8764,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-1.827993370840807</v>
+        <v>-1.80768233338702</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8772,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.4074378136962097</v>
+        <v>0.4093378136962097</v>
       </c>
       <c r="C92">
-        <v>-0.4739839732140756</v>
+        <v>-0.5147302896426491</v>
       </c>
       <c r="D92">
-        <v>0.8859160267859245</v>
+        <v>0.8832797103573512</v>
       </c>
       <c r="E92">
-        <v>3.0989</v>
+        <v>3.13701</v>
       </c>
       <c r="F92">
-        <v>3.4299</v>
+        <v>3.46801</v>
       </c>
       <c r="G92">
         <v>2.07</v>
@@ -8808,37 +8819,37 @@
         <v>-1.462</v>
       </c>
       <c r="M92">
-        <v>0.80877042</v>
+        <v>0.817756758</v>
       </c>
       <c r="N92">
-        <v>-2.27077042</v>
+        <v>-2.279756758</v>
       </c>
       <c r="O92">
-        <v>-0.6812311259999999</v>
+        <v>-0.6839270274</v>
       </c>
       <c r="P92">
-        <v>-1.589539294</v>
+        <v>-1.5958297306</v>
       </c>
       <c r="Q92">
-        <v>0.1904607060000001</v>
+        <v>0.1841702694</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.801299102587917</v>
+        <v>0.885243447319908</v>
       </c>
       <c r="T92">
-        <v>17.44801622604889</v>
+        <v>19.38668469560988</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.5423047000161059</v>
+        <v>-0.5363453077082366</v>
       </c>
       <c r="W92">
-        <v>0.3636754482637978</v>
+        <v>0.3622702235576022</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8846,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-1.80768233338702</v>
+        <v>-1.787817692360789</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8854,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.4093378136962097</v>
+        <v>0.4112378136962097</v>
       </c>
       <c r="C93">
-        <v>-0.5147302896426491</v>
+        <v>-0.5554609622785645</v>
       </c>
       <c r="D93">
-        <v>0.8832797103573512</v>
+        <v>0.8806590377214357</v>
       </c>
       <c r="E93">
-        <v>3.13701</v>
+        <v>3.17512</v>
       </c>
       <c r="F93">
-        <v>3.46801</v>
+        <v>3.50612</v>
       </c>
       <c r="G93">
         <v>2.07</v>
@@ -8890,37 +8901,37 @@
         <v>-1.462</v>
       </c>
       <c r="M93">
-        <v>0.817756758</v>
+        <v>0.8267430960000001</v>
       </c>
       <c r="N93">
-        <v>-2.279756758</v>
+        <v>-2.288743096</v>
       </c>
       <c r="O93">
-        <v>-0.6839270274</v>
+        <v>-0.6866229288</v>
       </c>
       <c r="P93">
-        <v>-1.5958297306</v>
+        <v>-1.6021201672</v>
       </c>
       <c r="Q93">
-        <v>0.1841702694</v>
+        <v>0.1778798327999997</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.885243447319908</v>
+        <v>0.9901738782348968</v>
       </c>
       <c r="T93">
-        <v>19.38668469560988</v>
+        <v>21.81002028256113</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.5363453077082366</v>
+        <v>-0.53051546740706</v>
       </c>
       <c r="W93">
-        <v>0.3622702235576022</v>
+        <v>0.3608955472145848</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8928,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-1.787817692360789</v>
+        <v>-1.768384891356867</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8936,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.4112378136962097</v>
+        <v>0.4131378136962097</v>
       </c>
       <c r="C94">
-        <v>-0.5554609622785645</v>
+        <v>-0.5961761299543364</v>
       </c>
       <c r="D94">
-        <v>0.8806590377214357</v>
+        <v>0.8780538700456639</v>
       </c>
       <c r="E94">
-        <v>3.17512</v>
+        <v>3.21323</v>
       </c>
       <c r="F94">
-        <v>3.50612</v>
+        <v>3.54423</v>
       </c>
       <c r="G94">
         <v>2.07</v>
@@ -8972,37 +8983,37 @@
         <v>-1.462</v>
       </c>
       <c r="M94">
-        <v>0.8267430960000001</v>
+        <v>0.8357294340000001</v>
       </c>
       <c r="N94">
-        <v>-2.288743096</v>
+        <v>-2.297729434</v>
       </c>
       <c r="O94">
-        <v>-0.6866229288</v>
+        <v>-0.6893188302</v>
       </c>
       <c r="P94">
-        <v>-1.6021201672</v>
+        <v>-1.6084106038</v>
       </c>
       <c r="Q94">
-        <v>0.1778798327999997</v>
+        <v>0.1715893962000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9901738782348968</v>
+        <v>1.125084432268454</v>
       </c>
       <c r="T94">
-        <v>21.81002028256113</v>
+        <v>24.92573746578415</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.53051546740706</v>
+        <v>-0.5248110000155862</v>
       </c>
       <c r="W94">
-        <v>0.3608955472145848</v>
+        <v>0.3595504338036753</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9010,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-1.768384891356867</v>
+        <v>-1.749370000051954</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9018,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.4131378136962097</v>
+        <v>0.4150378136962097</v>
       </c>
       <c r="C95">
-        <v>-0.5961761299543364</v>
+        <v>-0.6368759298645466</v>
       </c>
       <c r="D95">
-        <v>0.8780538700456639</v>
+        <v>0.8754640701354539</v>
       </c>
       <c r="E95">
-        <v>3.21323</v>
+        <v>3.25134</v>
       </c>
       <c r="F95">
-        <v>3.54423</v>
+        <v>3.58234</v>
       </c>
       <c r="G95">
         <v>2.07</v>
@@ -9054,37 +9065,37 @@
         <v>-1.462</v>
       </c>
       <c r="M95">
-        <v>0.8357294340000001</v>
+        <v>0.8447157720000001</v>
       </c>
       <c r="N95">
-        <v>-2.297729434</v>
+        <v>-2.306715772</v>
       </c>
       <c r="O95">
-        <v>-0.6893188302</v>
+        <v>-0.6920147315999999</v>
       </c>
       <c r="P95">
-        <v>-1.6084106038</v>
+        <v>-1.6147010404</v>
       </c>
       <c r="Q95">
-        <v>0.1715893962000001</v>
+        <v>0.1652989596000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.125084432268454</v>
+        <v>1.304965170979863</v>
       </c>
       <c r="T95">
-        <v>24.92573746578415</v>
+        <v>29.08002704341484</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.5248110000155862</v>
+        <v>-0.5192279042707396</v>
       </c>
       <c r="W95">
-        <v>0.3595504338036753</v>
+        <v>0.3582339398270404</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9092,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-1.749370000051954</v>
+        <v>-1.730759680902465</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9100,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.4150378136962097</v>
+        <v>0.4169378136962097</v>
       </c>
       <c r="C96">
-        <v>-0.6368759298645466</v>
+        <v>-0.6775604975899272</v>
       </c>
       <c r="D96">
-        <v>0.8754640701354539</v>
+        <v>0.8728895024100735</v>
       </c>
       <c r="E96">
-        <v>3.25134</v>
+        <v>3.28945</v>
       </c>
       <c r="F96">
-        <v>3.58234</v>
+        <v>3.62045</v>
       </c>
       <c r="G96">
         <v>2.07</v>
@@ -9136,37 +9147,37 @@
         <v>-1.462</v>
       </c>
       <c r="M96">
-        <v>0.8447157720000001</v>
+        <v>0.8537021100000002</v>
       </c>
       <c r="N96">
-        <v>-2.306715772</v>
+        <v>-2.31570211</v>
       </c>
       <c r="O96">
-        <v>-0.6920147315999999</v>
+        <v>-0.694710633</v>
       </c>
       <c r="P96">
-        <v>-1.6147010404</v>
+        <v>-1.620991477</v>
       </c>
       <c r="Q96">
-        <v>0.1652989596000001</v>
+        <v>0.159008523</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.304965170979863</v>
+        <v>1.556798205175836</v>
       </c>
       <c r="T96">
-        <v>29.08002704341484</v>
+        <v>34.89603245209783</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.5192279042707396</v>
+        <v>-0.5137623473836792</v>
       </c>
       <c r="W96">
-        <v>0.3582339398270404</v>
+        <v>0.3569451615130716</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9174,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-1.730759680902465</v>
+        <v>-1.712541157945597</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9182,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.4169378136962097</v>
+        <v>0.4188378136962097</v>
       </c>
       <c r="C97">
-        <v>-0.6775604975899272</v>
+        <v>-0.7182299671210211</v>
       </c>
       <c r="D97">
-        <v>0.8728895024100735</v>
+        <v>0.8703300328789794</v>
       </c>
       <c r="E97">
-        <v>3.28945</v>
+        <v>3.32756</v>
       </c>
       <c r="F97">
-        <v>3.62045</v>
+        <v>3.65856</v>
       </c>
       <c r="G97">
         <v>2.07</v>
@@ -9218,37 +9229,37 @@
         <v>-1.462</v>
       </c>
       <c r="M97">
-        <v>0.8537021100000002</v>
+        <v>0.862688448</v>
       </c>
       <c r="N97">
-        <v>-2.31570211</v>
+        <v>-2.324688448</v>
       </c>
       <c r="O97">
-        <v>-0.694710633</v>
+        <v>-0.6974065343999999</v>
       </c>
       <c r="P97">
-        <v>-1.620991477</v>
+        <v>-1.6272819136</v>
       </c>
       <c r="Q97">
-        <v>0.159008523</v>
+        <v>0.1527180864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.556798205175836</v>
+        <v>1.934547756469796</v>
       </c>
       <c r="T97">
-        <v>34.89603245209783</v>
+        <v>43.6200405651223</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.5137623473836792</v>
+        <v>-0.5084106562650993</v>
       </c>
       <c r="W97">
-        <v>0.3569451615130716</v>
+        <v>0.3556832327473104</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9256,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-1.712541157945597</v>
+        <v>-1.694702187550331</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9264,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.4188378136962096</v>
+        <v>0.4207378136962097</v>
       </c>
       <c r="C98">
-        <v>-0.7182299671210206</v>
+        <v>-0.7588844708814291</v>
       </c>
       <c r="D98">
-        <v>0.8703300328789794</v>
+        <v>0.8677855291185708</v>
       </c>
       <c r="E98">
-        <v>3.32756</v>
+        <v>3.36567</v>
       </c>
       <c r="F98">
-        <v>3.65856</v>
+        <v>3.69667</v>
       </c>
       <c r="G98">
         <v>2.07</v>
@@ -9300,37 +9311,37 @@
         <v>-1.462</v>
       </c>
       <c r="M98">
-        <v>0.8626884479999999</v>
+        <v>0.8716747859999999</v>
       </c>
       <c r="N98">
-        <v>-2.324688448</v>
+        <v>-2.333674786</v>
       </c>
       <c r="O98">
-        <v>-0.6974065343999999</v>
+        <v>-0.7001024358</v>
       </c>
       <c r="P98">
-        <v>-1.6272819136</v>
+        <v>-1.6335723502</v>
       </c>
       <c r="Q98">
-        <v>0.1527180864</v>
+        <v>0.1464276497999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.934547756469791</v>
+        <v>2.564130341959721</v>
       </c>
       <c r="T98">
-        <v>43.62004056512219</v>
+        <v>58.16005408682959</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.5084106562650993</v>
+        <v>-0.5031693092932942</v>
       </c>
       <c r="W98">
-        <v>0.3556832327473104</v>
+        <v>0.3544473231313588</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9338,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-1.694702187550331</v>
+        <v>-1.677231030977647</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9346,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.4207378136962097</v>
+        <v>0.4226378136962097</v>
       </c>
       <c r="C99">
-        <v>-0.7588844708814291</v>
+        <v>-0.7995241397506474</v>
       </c>
       <c r="D99">
-        <v>0.8677855291185708</v>
+        <v>0.8652558602493524</v>
       </c>
       <c r="E99">
-        <v>3.36567</v>
+        <v>3.40378</v>
       </c>
       <c r="F99">
-        <v>3.69667</v>
+        <v>3.73478</v>
       </c>
       <c r="G99">
         <v>2.07</v>
@@ -9382,37 +9393,37 @@
         <v>-1.462</v>
       </c>
       <c r="M99">
-        <v>0.8716747859999999</v>
+        <v>0.880661124</v>
       </c>
       <c r="N99">
-        <v>-2.333674786</v>
+        <v>-2.342661124</v>
       </c>
       <c r="O99">
-        <v>-0.7001024358</v>
+        <v>-0.7027983372000001</v>
       </c>
       <c r="P99">
-        <v>-1.6335723502</v>
+        <v>-1.6398627868</v>
       </c>
       <c r="Q99">
-        <v>0.1464276497999999</v>
+        <v>0.1401372131999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.564130341959721</v>
+        <v>3.823295512939582</v>
       </c>
       <c r="T99">
-        <v>58.16005408682959</v>
+        <v>87.24008113024438</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.5031693092932942</v>
+        <v>-0.4980349285862197</v>
       </c>
       <c r="W99">
-        <v>0.3544473231313588</v>
+        <v>0.3532366361606306</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9420,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-1.677231030977647</v>
+        <v>-1.660116428620733</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9428,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.4226378136962097</v>
+        <v>0.4245378136962097</v>
       </c>
       <c r="C100">
-        <v>-0.7995241397506474</v>
+        <v>-0.8401491030865085</v>
       </c>
       <c r="D100">
-        <v>0.8652558602493524</v>
+        <v>0.8627408969134917</v>
       </c>
       <c r="E100">
-        <v>3.40378</v>
+        <v>3.44189</v>
       </c>
       <c r="F100">
-        <v>3.73478</v>
+        <v>3.77289</v>
       </c>
       <c r="G100">
         <v>2.07</v>
@@ -9464,37 +9475,37 @@
         <v>-1.462</v>
       </c>
       <c r="M100">
-        <v>0.880661124</v>
+        <v>0.889647462</v>
       </c>
       <c r="N100">
-        <v>-2.342661124</v>
+        <v>-2.351647462</v>
       </c>
       <c r="O100">
-        <v>-0.7027983372000001</v>
+        <v>-0.7054942385999999</v>
       </c>
       <c r="P100">
-        <v>-1.6398627868</v>
+        <v>-1.6461532234</v>
       </c>
       <c r="Q100">
-        <v>0.1401372131999998</v>
+        <v>0.1338467766000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.823295512939582</v>
+        <v>7.600791025879164</v>
       </c>
       <c r="T100">
-        <v>87.24008113024438</v>
+        <v>174.4801622604888</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.4980349285862197</v>
+        <v>-0.4930042727419144</v>
       </c>
       <c r="W100">
-        <v>0.3532366361606306</v>
+        <v>0.3520504075125434</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9502,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-1.660116428620733</v>
+        <v>-1.643347575806382</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.4245378136962097</v>
-      </c>
-      <c r="C101">
-        <v>-0.8401491030865085</v>
-      </c>
-      <c r="D101">
-        <v>0.8627408969134917</v>
-      </c>
-      <c r="E101">
-        <v>3.44189</v>
-      </c>
-      <c r="F101">
-        <v>3.77289</v>
-      </c>
-      <c r="G101">
-        <v>2.07</v>
-      </c>
-      <c r="H101">
-        <v>3.48</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.318</v>
-      </c>
-      <c r="K101">
-        <v>1.78</v>
-      </c>
-      <c r="L101">
-        <v>-1.462</v>
-      </c>
-      <c r="M101">
-        <v>0.889647462</v>
-      </c>
-      <c r="N101">
-        <v>-2.351647462</v>
-      </c>
-      <c r="O101">
-        <v>-0.7054942385999999</v>
-      </c>
-      <c r="P101">
-        <v>-1.6461532234</v>
-      </c>
-      <c r="Q101">
-        <v>0.1338467766000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.600791025879164</v>
-      </c>
-      <c r="T101">
-        <v>174.4801622604888</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.4930042727419144</v>
-      </c>
-      <c r="W101">
-        <v>0.3520504075125434</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-1.643347575806382</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
